--- a/grupos/6ALCM - Estadisticos 20222.xlsx
+++ b/grupos/6ALCM - Estadisticos 20222.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="305" uniqueCount="161">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="155">
   <si>
     <t>Materia</t>
   </si>
@@ -193,24 +193,6 @@
   </si>
   <si>
     <t>Por_Blancos</t>
-  </si>
-  <si>
-    <t>TEMAS DE CIENCIAS DE LA SALUD</t>
-  </si>
-  <si>
-    <t>TEMAS DE FÍSICA</t>
-  </si>
-  <si>
-    <t>LITERATURA</t>
-  </si>
-  <si>
-    <t>INTRODUCCIÓN AL DERECHO</t>
-  </si>
-  <si>
-    <t>HISTORIA</t>
-  </si>
-  <si>
-    <t>TEMAS DE CIENCIAS SOCIALES</t>
   </si>
   <si>
     <t>Desc Desc Desc</t>
@@ -5728,7 +5710,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J13"/>
+  <dimension ref="A1:J7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="50.7109375" customWidth="1"/>
@@ -5768,313 +5750,193 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" t="s">
         <v>58</v>
       </c>
-      <c r="B2" t="s">
-        <v>64</v>
-      </c>
       <c r="C2">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="D2">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>3</v>
+      </c>
+      <c r="F2">
+        <v>91.18000000000001</v>
+      </c>
+      <c r="G2">
+        <v>8.82</v>
+      </c>
+      <c r="H2">
+        <v>7.6</v>
       </c>
       <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
         <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" t="s">
         <v>59</v>
       </c>
-      <c r="B3" t="s">
-        <v>64</v>
-      </c>
       <c r="C3">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="D3">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="F3">
+        <v>94.12</v>
+      </c>
+      <c r="G3">
+        <v>5.88</v>
+      </c>
+      <c r="H3">
+        <v>8.1</v>
       </c>
       <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
         <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>60</v>
+        <v>9</v>
       </c>
       <c r="B4" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="C4">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="D4">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="F4">
+        <v>97.06</v>
+      </c>
+      <c r="G4">
+        <v>2.94</v>
+      </c>
+      <c r="H4">
+        <v>9</v>
       </c>
       <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
         <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>61</v>
+        <v>7</v>
       </c>
       <c r="B5" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="C5">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="D5">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="E5">
         <v>0</v>
       </c>
+      <c r="F5">
+        <v>100</v>
+      </c>
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5">
+        <v>9.300000000000001</v>
+      </c>
       <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
         <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>62</v>
+        <v>6</v>
       </c>
       <c r="B6" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="C6">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="D6">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="E6">
         <v>0</v>
       </c>
+      <c r="F6">
+        <v>100</v>
+      </c>
+      <c r="G6">
+        <v>0</v>
+      </c>
+      <c r="H6">
+        <v>9</v>
+      </c>
       <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
         <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>63</v>
+        <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="C7">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="D7">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="E7">
         <v>0</v>
       </c>
+      <c r="F7">
+        <v>100</v>
+      </c>
+      <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="H7">
+        <v>9</v>
+      </c>
       <c r="I7">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:10">
-      <c r="A8" t="s">
-        <v>8</v>
-      </c>
-      <c r="B8" t="s">
-        <v>64</v>
-      </c>
-      <c r="C8">
-        <v>34</v>
-      </c>
-      <c r="D8">
-        <v>31</v>
-      </c>
-      <c r="E8">
-        <v>3</v>
-      </c>
-      <c r="F8">
-        <v>91.18000000000001</v>
-      </c>
-      <c r="G8">
-        <v>8.82</v>
-      </c>
-      <c r="H8">
-        <v>7.6</v>
-      </c>
-      <c r="I8">
-        <v>0</v>
-      </c>
-      <c r="J8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10">
-      <c r="A9" t="s">
-        <v>10</v>
-      </c>
-      <c r="B9" t="s">
-        <v>65</v>
-      </c>
-      <c r="C9">
-        <v>34</v>
-      </c>
-      <c r="D9">
-        <v>32</v>
-      </c>
-      <c r="E9">
-        <v>2</v>
-      </c>
-      <c r="F9">
-        <v>94.12</v>
-      </c>
-      <c r="G9">
-        <v>5.88</v>
-      </c>
-      <c r="H9">
-        <v>8.1</v>
-      </c>
-      <c r="I9">
-        <v>0</v>
-      </c>
-      <c r="J9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10">
-      <c r="A10" t="s">
-        <v>9</v>
-      </c>
-      <c r="B10" t="s">
-        <v>64</v>
-      </c>
-      <c r="C10">
-        <v>34</v>
-      </c>
-      <c r="D10">
-        <v>33</v>
-      </c>
-      <c r="E10">
-        <v>1</v>
-      </c>
-      <c r="F10">
-        <v>97.06</v>
-      </c>
-      <c r="G10">
-        <v>2.94</v>
-      </c>
-      <c r="H10">
-        <v>9</v>
-      </c>
-      <c r="I10">
-        <v>0</v>
-      </c>
-      <c r="J10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10">
-      <c r="A11" t="s">
-        <v>7</v>
-      </c>
-      <c r="B11" t="s">
-        <v>66</v>
-      </c>
-      <c r="C11">
-        <v>34</v>
-      </c>
-      <c r="D11">
-        <v>34</v>
-      </c>
-      <c r="E11">
-        <v>0</v>
-      </c>
-      <c r="F11">
-        <v>100</v>
-      </c>
-      <c r="G11">
-        <v>0</v>
-      </c>
-      <c r="H11">
-        <v>9.300000000000001</v>
-      </c>
-      <c r="I11">
-        <v>0</v>
-      </c>
-      <c r="J11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10">
-      <c r="A12" t="s">
-        <v>6</v>
-      </c>
-      <c r="B12" t="s">
-        <v>64</v>
-      </c>
-      <c r="C12">
-        <v>34</v>
-      </c>
-      <c r="D12">
-        <v>34</v>
-      </c>
-      <c r="E12">
-        <v>0</v>
-      </c>
-      <c r="F12">
-        <v>100</v>
-      </c>
-      <c r="G12">
-        <v>0</v>
-      </c>
-      <c r="H12">
-        <v>9</v>
-      </c>
-      <c r="I12">
-        <v>0</v>
-      </c>
-      <c r="J12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10">
-      <c r="A13" t="s">
-        <v>5</v>
-      </c>
-      <c r="B13" t="s">
-        <v>64</v>
-      </c>
-      <c r="C13">
-        <v>34</v>
-      </c>
-      <c r="D13">
-        <v>34</v>
-      </c>
-      <c r="E13">
-        <v>0</v>
-      </c>
-      <c r="F13">
-        <v>100</v>
-      </c>
-      <c r="G13">
-        <v>0</v>
-      </c>
-      <c r="H13">
-        <v>9</v>
-      </c>
-      <c r="I13">
-        <v>0</v>
-      </c>
-      <c r="J13">
+      <c r="J7">
         <v>0</v>
       </c>
     </row>
@@ -6094,16 +5956,16 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>0</v>
@@ -6128,16 +5990,16 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>56</v>
@@ -6148,13 +6010,13 @@
         <v>20330051920187</v>
       </c>
       <c r="B2" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="C2" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="D2" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -6165,13 +6027,13 @@
         <v>20330051920220</v>
       </c>
       <c r="B3" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="C3" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="D3" t="s">
-        <v>128</v>
+        <v>122</v>
       </c>
       <c r="E3">
         <v>0</v>
@@ -6182,13 +6044,13 @@
         <v>20330051920221</v>
       </c>
       <c r="B4" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="C4" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="D4" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="E4">
         <v>0</v>
@@ -6199,13 +6061,13 @@
         <v>20330051920374</v>
       </c>
       <c r="B5" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="C5" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="D5" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="E5">
         <v>0</v>
@@ -6216,13 +6078,13 @@
         <v>20330051920223</v>
       </c>
       <c r="B6" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="C6" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="D6" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="E6">
         <v>0</v>
@@ -6233,13 +6095,13 @@
         <v>20330051920224</v>
       </c>
       <c r="B7" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="C7" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="D7" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="E7">
         <v>0</v>
@@ -6250,13 +6112,13 @@
         <v>20330051920225</v>
       </c>
       <c r="B8" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="C8" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="D8" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="E8">
         <v>0</v>
@@ -6267,13 +6129,13 @@
         <v>20330051920375</v>
       </c>
       <c r="B9" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="C9" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="D9" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="E9">
         <v>0</v>
@@ -6284,13 +6146,13 @@
         <v>20330051920226</v>
       </c>
       <c r="B10" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="C10" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="D10" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="E10">
         <v>0</v>
@@ -6301,13 +6163,13 @@
         <v>20330051920227</v>
       </c>
       <c r="B11" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="C11" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="D11" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="E11">
         <v>0</v>
@@ -6318,13 +6180,13 @@
         <v>20330051920228</v>
       </c>
       <c r="B12" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="C12" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="D12" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="E12">
         <v>0</v>
@@ -6335,13 +6197,13 @@
         <v>20330051920229</v>
       </c>
       <c r="B13" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="C13" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="D13" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="E13">
         <v>0</v>
@@ -6352,13 +6214,13 @@
         <v>20330051920230</v>
       </c>
       <c r="B14" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="C14" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="D14" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="E14">
         <v>0</v>
@@ -6369,13 +6231,13 @@
         <v>20330051920231</v>
       </c>
       <c r="B15" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="C15" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="D15" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="E15">
         <v>0</v>
@@ -6386,13 +6248,13 @@
         <v>20330051920232</v>
       </c>
       <c r="B16" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="C16" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="D16" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="E16">
         <v>0</v>
@@ -6403,13 +6265,13 @@
         <v>20330051920233</v>
       </c>
       <c r="B17" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="C17" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="D17" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
       <c r="E17">
         <v>0</v>
@@ -6420,13 +6282,13 @@
         <v>20330051920234</v>
       </c>
       <c r="B18" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="C18" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="D18" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="E18">
         <v>0</v>
@@ -6437,13 +6299,13 @@
         <v>20330051920376</v>
       </c>
       <c r="B19" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="C19" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="D19" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="E19">
         <v>0</v>
@@ -6454,13 +6316,13 @@
         <v>20330051920236</v>
       </c>
       <c r="B20" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="C20" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="D20" t="s">
-        <v>145</v>
+        <v>139</v>
       </c>
       <c r="E20">
         <v>0</v>
@@ -6471,13 +6333,13 @@
         <v>20330051920238</v>
       </c>
       <c r="B21" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="C21" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="D21" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="E21">
         <v>0</v>
@@ -6488,13 +6350,13 @@
         <v>20330051920239</v>
       </c>
       <c r="B22" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="C22" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="D22" t="s">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="E22">
         <v>0</v>
@@ -6505,13 +6367,13 @@
         <v>20330051920240</v>
       </c>
       <c r="B23" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="C23" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="D23" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="E23">
         <v>0</v>
@@ -6522,13 +6384,13 @@
         <v>20330051920241</v>
       </c>
       <c r="B24" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="C24" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="D24" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="E24">
         <v>0</v>
@@ -6539,13 +6401,13 @@
         <v>20330051920243</v>
       </c>
       <c r="B25" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="C25" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="D25" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="E25">
         <v>0</v>
@@ -6556,13 +6418,13 @@
         <v>20330051920244</v>
       </c>
       <c r="B26" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="C26" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="D26" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="E26">
         <v>0</v>
@@ -6573,13 +6435,13 @@
         <v>20330051920248</v>
       </c>
       <c r="B27" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="C27" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="D27" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="E27">
         <v>0</v>
@@ -6590,13 +6452,13 @@
         <v>20330051920249</v>
       </c>
       <c r="B28" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="C28" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="D28" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="E28">
         <v>0</v>
@@ -6607,13 +6469,13 @@
         <v>20330051920250</v>
       </c>
       <c r="B29" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="C29" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="D29" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="E29">
         <v>0</v>
@@ -6624,13 +6486,13 @@
         <v>20330051920251</v>
       </c>
       <c r="B30" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="C30" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="D30" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="E30">
         <v>0</v>
@@ -6641,13 +6503,13 @@
         <v>20330051920252</v>
       </c>
       <c r="B31" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="C31" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="D31" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="E31">
         <v>0</v>
@@ -6658,13 +6520,13 @@
         <v>20330051920253</v>
       </c>
       <c r="B32" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="C32" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="D32" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="E32">
         <v>0</v>
@@ -6675,13 +6537,13 @@
         <v>20330051920256</v>
       </c>
       <c r="B33" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="C33" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="D33" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="E33">
         <v>0</v>
@@ -6692,13 +6554,13 @@
         <v>20330051920257</v>
       </c>
       <c r="B34" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="C34" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="D34" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="E34">
         <v>0</v>
@@ -6709,13 +6571,13 @@
         <v>20330051920258</v>
       </c>
       <c r="B35" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="C35" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="D35" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="E35">
         <v>0</v>
@@ -6737,16 +6599,16 @@
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>0</v>
@@ -6763,19 +6625,19 @@
         <v>20330051920236</v>
       </c>
       <c r="B2" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="C2" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="D2" t="s">
-        <v>145</v>
+        <v>139</v>
       </c>
       <c r="E2" t="s">
         <v>9</v>
       </c>
       <c r="F2" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -6786,19 +6648,19 @@
         <v>20330051920236</v>
       </c>
       <c r="B3" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="C3" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="D3" t="s">
-        <v>145</v>
+        <v>139</v>
       </c>
       <c r="E3" t="s">
         <v>10</v>
       </c>
       <c r="F3" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -6809,19 +6671,19 @@
         <v>20330051920226</v>
       </c>
       <c r="B4" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="C4" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="D4" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -6832,19 +6694,19 @@
         <v>20330051920240</v>
       </c>
       <c r="B5" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="C5" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="D5" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -6855,19 +6717,19 @@
         <v>20330051920244</v>
       </c>
       <c r="B6" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="C6" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="D6" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="E6" t="s">
         <v>10</v>
       </c>
       <c r="F6" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -6878,19 +6740,19 @@
         <v>20330051920251</v>
       </c>
       <c r="B7" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="C7" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="D7" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="G7">
         <v>5</v>

--- a/grupos/6ALCM - Estadisticos 20222.xlsx
+++ b/grupos/6ALCM - Estadisticos 20222.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="155">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="157">
   <si>
     <t>Materia</t>
   </si>
@@ -195,13 +195,19 @@
     <t>Por_Blancos</t>
   </si>
   <si>
-    <t>Desc Desc Desc</t>
+    <t>Velasco Sánchez David</t>
   </si>
   <si>
     <t>Ochoa Martínez Mayeli</t>
   </si>
   <si>
+    <t>Rivera Cruz Ezequiel</t>
+  </si>
+  <si>
     <t>Martínez Castillo Columba</t>
+  </si>
+  <si>
+    <t>Ángel Martínez Gerson Hermenegildo</t>
   </si>
   <si>
     <t>NC</t>
@@ -5817,7 +5823,7 @@
         <v>9</v>
       </c>
       <c r="B4" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C4">
         <v>34</v>
@@ -5849,7 +5855,7 @@
         <v>7</v>
       </c>
       <c r="B5" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C5">
         <v>34</v>
@@ -5881,7 +5887,7 @@
         <v>6</v>
       </c>
       <c r="B6" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="C6">
         <v>34</v>
@@ -5913,7 +5919,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="C7">
         <v>34</v>
@@ -5956,16 +5962,16 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>0</v>
@@ -5990,16 +5996,16 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>56</v>
@@ -6010,13 +6016,13 @@
         <v>20330051920187</v>
       </c>
       <c r="B2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C2" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -6027,13 +6033,13 @@
         <v>20330051920220</v>
       </c>
       <c r="B3" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C3" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D3" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="E3">
         <v>0</v>
@@ -6044,13 +6050,13 @@
         <v>20330051920221</v>
       </c>
       <c r="B4" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C4" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D4" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="E4">
         <v>0</v>
@@ -6061,13 +6067,13 @@
         <v>20330051920374</v>
       </c>
       <c r="B5" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C5" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="D5" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E5">
         <v>0</v>
@@ -6078,13 +6084,13 @@
         <v>20330051920223</v>
       </c>
       <c r="B6" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C6" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="D6" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="E6">
         <v>0</v>
@@ -6095,13 +6101,13 @@
         <v>20330051920224</v>
       </c>
       <c r="B7" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C7" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D7" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E7">
         <v>0</v>
@@ -6112,13 +6118,13 @@
         <v>20330051920225</v>
       </c>
       <c r="B8" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C8" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="D8" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="E8">
         <v>0</v>
@@ -6129,13 +6135,13 @@
         <v>20330051920375</v>
       </c>
       <c r="B9" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C9" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="D9" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E9">
         <v>0</v>
@@ -6146,13 +6152,13 @@
         <v>20330051920226</v>
       </c>
       <c r="B10" t="s">
+        <v>75</v>
+      </c>
+      <c r="C10" t="s">
         <v>73</v>
       </c>
-      <c r="C10" t="s">
-        <v>71</v>
-      </c>
       <c r="D10" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="E10">
         <v>0</v>
@@ -6163,13 +6169,13 @@
         <v>20330051920227</v>
       </c>
       <c r="B11" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C11" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D11" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="E11">
         <v>0</v>
@@ -6180,13 +6186,13 @@
         <v>20330051920228</v>
       </c>
       <c r="B12" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C12" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="D12" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="E12">
         <v>0</v>
@@ -6197,13 +6203,13 @@
         <v>20330051920229</v>
       </c>
       <c r="B13" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C13" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D13" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E13">
         <v>0</v>
@@ -6214,13 +6220,13 @@
         <v>20330051920230</v>
       </c>
       <c r="B14" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C14" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="D14" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="E14">
         <v>0</v>
@@ -6231,13 +6237,13 @@
         <v>20330051920231</v>
       </c>
       <c r="B15" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C15" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="D15" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="E15">
         <v>0</v>
@@ -6248,13 +6254,13 @@
         <v>20330051920232</v>
       </c>
       <c r="B16" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="C16" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="D16" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="E16">
         <v>0</v>
@@ -6265,13 +6271,13 @@
         <v>20330051920233</v>
       </c>
       <c r="B17" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C17" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="D17" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="E17">
         <v>0</v>
@@ -6282,13 +6288,13 @@
         <v>20330051920234</v>
       </c>
       <c r="B18" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="C18" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="D18" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="E18">
         <v>0</v>
@@ -6299,13 +6305,13 @@
         <v>20330051920376</v>
       </c>
       <c r="B19" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C19" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="D19" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="E19">
         <v>0</v>
@@ -6316,13 +6322,13 @@
         <v>20330051920236</v>
       </c>
       <c r="B20" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C20" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="D20" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="E20">
         <v>0</v>
@@ -6333,13 +6339,13 @@
         <v>20330051920238</v>
       </c>
       <c r="B21" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C21" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="D21" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="E21">
         <v>0</v>
@@ -6350,13 +6356,13 @@
         <v>20330051920239</v>
       </c>
       <c r="B22" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C22" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D22" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="E22">
         <v>0</v>
@@ -6367,13 +6373,13 @@
         <v>20330051920240</v>
       </c>
       <c r="B23" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C23" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D23" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="E23">
         <v>0</v>
@@ -6384,13 +6390,13 @@
         <v>20330051920241</v>
       </c>
       <c r="B24" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C24" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="D24" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="E24">
         <v>0</v>
@@ -6401,13 +6407,13 @@
         <v>20330051920243</v>
       </c>
       <c r="B25" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C25" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="D25" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="E25">
         <v>0</v>
@@ -6418,13 +6424,13 @@
         <v>20330051920244</v>
       </c>
       <c r="B26" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C26" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="D26" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="E26">
         <v>0</v>
@@ -6435,13 +6441,13 @@
         <v>20330051920248</v>
       </c>
       <c r="B27" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C27" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D27" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="E27">
         <v>0</v>
@@ -6452,13 +6458,13 @@
         <v>20330051920249</v>
       </c>
       <c r="B28" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C28" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="D28" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="E28">
         <v>0</v>
@@ -6469,13 +6475,13 @@
         <v>20330051920250</v>
       </c>
       <c r="B29" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C29" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="D29" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="E29">
         <v>0</v>
@@ -6486,13 +6492,13 @@
         <v>20330051920251</v>
       </c>
       <c r="B30" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C30" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="D30" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="E30">
         <v>0</v>
@@ -6503,13 +6509,13 @@
         <v>20330051920252</v>
       </c>
       <c r="B31" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C31" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="D31" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="E31">
         <v>0</v>
@@ -6520,13 +6526,13 @@
         <v>20330051920253</v>
       </c>
       <c r="B32" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C32" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="D32" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="E32">
         <v>0</v>
@@ -6537,13 +6543,13 @@
         <v>20330051920256</v>
       </c>
       <c r="B33" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C33" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="D33" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="E33">
         <v>0</v>
@@ -6554,13 +6560,13 @@
         <v>20330051920257</v>
       </c>
       <c r="B34" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C34" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="D34" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="E34">
         <v>0</v>
@@ -6571,13 +6577,13 @@
         <v>20330051920258</v>
       </c>
       <c r="B35" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="C35" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="D35" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E35">
         <v>0</v>
@@ -6599,16 +6605,16 @@
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>0</v>
@@ -6625,19 +6631,19 @@
         <v>20330051920236</v>
       </c>
       <c r="B2" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C2" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="D2" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="E2" t="s">
         <v>9</v>
       </c>
       <c r="F2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -6648,13 +6654,13 @@
         <v>20330051920236</v>
       </c>
       <c r="B3" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C3" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="D3" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="E3" t="s">
         <v>10</v>
@@ -6671,13 +6677,13 @@
         <v>20330051920226</v>
       </c>
       <c r="B4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C4" t="s">
         <v>73</v>
       </c>
-      <c r="C4" t="s">
-        <v>71</v>
-      </c>
       <c r="D4" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -6694,13 +6700,13 @@
         <v>20330051920240</v>
       </c>
       <c r="B5" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C5" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D5" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -6717,13 +6723,13 @@
         <v>20330051920244</v>
       </c>
       <c r="B6" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C6" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="D6" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="E6" t="s">
         <v>10</v>
@@ -6740,13 +6746,13 @@
         <v>20330051920251</v>
       </c>
       <c r="B7" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C7" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="D7" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>

--- a/grupos/6ALCM - Estadisticos 20222.xlsx
+++ b/grupos/6ALCM - Estadisticos 20222.xlsx
@@ -11,15 +11,14 @@
     <sheet name="Asistencias" sheetId="2" r:id="rId2"/>
     <sheet name="Totales" sheetId="3" r:id="rId3"/>
     <sheet name="Blancos" sheetId="4" r:id="rId4"/>
-    <sheet name="Totales Blanco" sheetId="5" r:id="rId5"/>
-    <sheet name="Rescatables" sheetId="6" r:id="rId6"/>
+    <sheet name="Rescatables" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="157">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="79">
   <si>
     <t>Materia</t>
   </si>
@@ -222,280 +221,49 @@
     <t>Nombres</t>
   </si>
   <si>
-    <t>ALVARADO</t>
-  </si>
-  <si>
-    <t>ARELLANO</t>
-  </si>
-  <si>
-    <t>ANGEL</t>
-  </si>
-  <si>
-    <t>BERISTAIN</t>
-  </si>
-  <si>
-    <t>CASTELLANOS</t>
-  </si>
-  <si>
-    <t>COLOHUA</t>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>MAZAHUA</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>DE LOS SANTOS</t>
   </si>
   <si>
     <t>CRUZ</t>
   </si>
   <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>HUERTA</t>
-  </si>
-  <si>
-    <t>JUSTO</t>
-  </si>
-  <si>
-    <t>LASTRE</t>
-  </si>
-  <si>
-    <t>LARRINAGA</t>
-  </si>
-  <si>
-    <t>LIMA</t>
-  </si>
-  <si>
-    <t>MAZAHUA</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>MACARIO</t>
-  </si>
-  <si>
-    <t>MENDOZA</t>
-  </si>
-  <si>
-    <t>OLTEHUA</t>
-  </si>
-  <si>
-    <t>PLIEGO</t>
-  </si>
-  <si>
-    <t>REYES</t>
-  </si>
-  <si>
-    <t>ROMAN</t>
-  </si>
-  <si>
-    <t>DE LOS SANTOS</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>TLECUILE</t>
-  </si>
-  <si>
-    <t>VARGAS</t>
-  </si>
-  <si>
-    <t>XOTLANIHUA</t>
-  </si>
-  <si>
-    <t>CIRUELO</t>
-  </si>
-  <si>
-    <t>MARIA</t>
-  </si>
-  <si>
-    <t>APALE</t>
-  </si>
-  <si>
-    <t>TEQUIHUATLE</t>
-  </si>
-  <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
-    <t>CONDE</t>
-  </si>
-  <si>
-    <t>IXMATLAHUA</t>
-  </si>
-  <si>
-    <t>CERVANTES</t>
-  </si>
-  <si>
-    <t>GALEOTE</t>
-  </si>
-  <si>
-    <t>JIMENEZ</t>
-  </si>
-  <si>
-    <t>SALGADO</t>
-  </si>
-  <si>
-    <t>ENRIQUEZ</t>
-  </si>
-  <si>
-    <t>LORENZO</t>
-  </si>
-  <si>
-    <t>PACHECO</t>
-  </si>
-  <si>
-    <t>SANTES</t>
-  </si>
-  <si>
-    <t>MARINERO</t>
-  </si>
-  <si>
     <t>ACEVEDO</t>
   </si>
   <si>
-    <t>CARRERA</t>
-  </si>
-  <si>
     <t>LOPEZ</t>
   </si>
   <si>
-    <t>LEON</t>
-  </si>
-  <si>
-    <t>OFICIAL</t>
-  </si>
-  <si>
-    <t>ANTONIO</t>
-  </si>
-  <si>
     <t>CALIHUA</t>
   </si>
   <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>QUIAHUA</t>
-  </si>
-  <si>
-    <t>VALLEJO</t>
-  </si>
-  <si>
-    <t>TETLA</t>
-  </si>
-  <si>
-    <t>FATIMA</t>
-  </si>
-  <si>
-    <t>VANELY JUDITH</t>
-  </si>
-  <si>
-    <t>JOSSELIN GUADALUPE</t>
-  </si>
-  <si>
-    <t>JOSE ISAIAS</t>
-  </si>
-  <si>
-    <t>JENNIFER</t>
-  </si>
-  <si>
-    <t>FERNANDA</t>
-  </si>
-  <si>
-    <t>JUAN ALBERTO</t>
-  </si>
-  <si>
-    <t>JENIFER</t>
-  </si>
-  <si>
     <t>JESSICA</t>
   </si>
   <si>
-    <t>VICTORINO</t>
-  </si>
-  <si>
-    <t>GERMAN ISAI</t>
-  </si>
-  <si>
-    <t>MARIA ISABEL</t>
-  </si>
-  <si>
-    <t>ARTURO</t>
-  </si>
-  <si>
-    <t>YAZMIN</t>
-  </si>
-  <si>
-    <t>EVELYN</t>
-  </si>
-  <si>
-    <t>ATENEA</t>
-  </si>
-  <si>
-    <t>GONZALO FEDERICO</t>
-  </si>
-  <si>
-    <t>MERARY MADAY</t>
-  </si>
-  <si>
     <t>GENARO RAFAEL</t>
   </si>
   <si>
-    <t>CAROLINA</t>
-  </si>
-  <si>
-    <t>PERLA MARITZA</t>
-  </si>
-  <si>
     <t>DIEGO</t>
   </si>
   <si>
-    <t>ITZEL</t>
-  </si>
-  <si>
-    <t>LISBETH ESMERALDA</t>
-  </si>
-  <si>
-    <t>VICTOR GAMALIEL</t>
-  </si>
-  <si>
-    <t>FERNANDO VADHIR</t>
-  </si>
-  <si>
-    <t>CYNTHIA AIDEE</t>
-  </si>
-  <si>
-    <t>FABIOLA</t>
-  </si>
-  <si>
     <t>ANGEL EMMANUEL</t>
-  </si>
-  <si>
-    <t>ARLET</t>
-  </si>
-  <si>
-    <t>ROSARIO</t>
-  </si>
-  <si>
-    <t>SAUL</t>
-  </si>
-  <si>
-    <t>SELINA</t>
-  </si>
-  <si>
-    <t>ERIKA</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.0\%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <sz val="11"/>
@@ -548,11 +316,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -993,10 +762,10 @@
         <v>9</v>
       </c>
       <c r="H4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J4">
         <v>-1</v>
@@ -1005,10 +774,10 @@
         <v>-1</v>
       </c>
       <c r="L4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N4">
         <v>-1</v>
@@ -1029,10 +798,10 @@
         <v>-1</v>
       </c>
       <c r="T4">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U4">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V4">
         <v>9</v>
@@ -1041,7 +810,7 @@
         <v>9</v>
       </c>
       <c r="X4">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y4">
         <v>9</v>
@@ -1070,10 +839,10 @@
         <v>8</v>
       </c>
       <c r="H5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J5">
         <v>-1</v>
@@ -1082,10 +851,10 @@
         <v>-1</v>
       </c>
       <c r="L5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N5">
         <v>-1</v>
@@ -1147,10 +916,10 @@
         <v>6</v>
       </c>
       <c r="H6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J6">
         <v>-1</v>
@@ -1159,10 +928,10 @@
         <v>-1</v>
       </c>
       <c r="L6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N6">
         <v>-1</v>
@@ -1183,7 +952,7 @@
         <v>-1</v>
       </c>
       <c r="T6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U6">
         <v>10</v>
@@ -1195,10 +964,10 @@
         <v>6</v>
       </c>
       <c r="X6">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y6">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7" spans="1:25">
@@ -1224,10 +993,10 @@
         <v>10</v>
       </c>
       <c r="H7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J7">
         <v>-1</v>
@@ -1236,10 +1005,10 @@
         <v>-1</v>
       </c>
       <c r="L7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N7">
         <v>-1</v>
@@ -1260,10 +1029,10 @@
         <v>-1</v>
       </c>
       <c r="T7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V7">
         <v>10</v>
@@ -1272,7 +1041,7 @@
         <v>9</v>
       </c>
       <c r="X7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y7">
         <v>10</v>
@@ -1301,10 +1070,10 @@
         <v>9</v>
       </c>
       <c r="H8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J8">
         <v>-1</v>
@@ -1313,10 +1082,10 @@
         <v>-1</v>
       </c>
       <c r="L8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N8">
         <v>-1</v>
@@ -1378,10 +1147,10 @@
         <v>8</v>
       </c>
       <c r="H9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J9">
         <v>-1</v>
@@ -1390,10 +1159,10 @@
         <v>-1</v>
       </c>
       <c r="L9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N9">
         <v>-1</v>
@@ -1414,10 +1183,10 @@
         <v>-1</v>
       </c>
       <c r="T9">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U9">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V9">
         <v>10</v>
@@ -1429,7 +1198,7 @@
         <v>9</v>
       </c>
       <c r="Y9">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="10" spans="1:25">
@@ -1455,10 +1224,10 @@
         <v>9</v>
       </c>
       <c r="H10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J10">
         <v>-1</v>
@@ -1467,10 +1236,10 @@
         <v>-1</v>
       </c>
       <c r="L10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N10">
         <v>-1</v>
@@ -1506,7 +1275,7 @@
         <v>9</v>
       </c>
       <c r="Y10">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="11" spans="1:25">
@@ -1532,10 +1301,10 @@
         <v>7</v>
       </c>
       <c r="H11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J11">
         <v>-1</v>
@@ -1544,10 +1313,10 @@
         <v>-1</v>
       </c>
       <c r="L11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N11">
         <v>-1</v>
@@ -1580,7 +1349,7 @@
         <v>5</v>
       </c>
       <c r="X11">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y11">
         <v>7</v>
@@ -1609,10 +1378,10 @@
         <v>9</v>
       </c>
       <c r="H12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J12">
         <v>-1</v>
@@ -1621,10 +1390,10 @@
         <v>-1</v>
       </c>
       <c r="L12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N12">
         <v>-1</v>
@@ -1686,10 +1455,10 @@
         <v>8</v>
       </c>
       <c r="H13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J13">
         <v>-1</v>
@@ -1698,10 +1467,10 @@
         <v>-1</v>
       </c>
       <c r="L13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N13">
         <v>-1</v>
@@ -1734,10 +1503,10 @@
         <v>5</v>
       </c>
       <c r="X13">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y13">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="14" spans="1:25">
@@ -1763,10 +1532,10 @@
         <v>10</v>
       </c>
       <c r="H14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J14">
         <v>-1</v>
@@ -1775,10 +1544,10 @@
         <v>-1</v>
       </c>
       <c r="L14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N14">
         <v>-1</v>
@@ -1840,10 +1609,10 @@
         <v>8</v>
       </c>
       <c r="H15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J15">
         <v>-1</v>
@@ -1852,10 +1621,10 @@
         <v>-1</v>
       </c>
       <c r="L15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N15">
         <v>-1</v>
@@ -1888,7 +1657,7 @@
         <v>7</v>
       </c>
       <c r="X15">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y15">
         <v>8</v>
@@ -1917,10 +1686,10 @@
         <v>9</v>
       </c>
       <c r="H16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J16">
         <v>-1</v>
@@ -1929,10 +1698,10 @@
         <v>-1</v>
       </c>
       <c r="L16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N16">
         <v>-1</v>
@@ -1994,10 +1763,10 @@
         <v>6</v>
       </c>
       <c r="H17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J17">
         <v>-1</v>
@@ -2006,10 +1775,10 @@
         <v>-1</v>
       </c>
       <c r="L17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N17">
         <v>-1</v>
@@ -2045,7 +1814,7 @@
         <v>9</v>
       </c>
       <c r="Y17">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="18" spans="1:25">
@@ -2071,10 +1840,10 @@
         <v>7</v>
       </c>
       <c r="H18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J18">
         <v>-1</v>
@@ -2083,10 +1852,10 @@
         <v>-1</v>
       </c>
       <c r="L18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N18">
         <v>-1</v>
@@ -2119,7 +1888,7 @@
         <v>7</v>
       </c>
       <c r="X18">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y18">
         <v>7</v>
@@ -2148,10 +1917,10 @@
         <v>8</v>
       </c>
       <c r="H19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J19">
         <v>-1</v>
@@ -2160,10 +1929,10 @@
         <v>-1</v>
       </c>
       <c r="L19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N19">
         <v>-1</v>
@@ -2196,10 +1965,10 @@
         <v>9</v>
       </c>
       <c r="X19">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y19">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="20" spans="1:25">
@@ -2225,10 +1994,10 @@
         <v>7</v>
       </c>
       <c r="H20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J20">
         <v>-1</v>
@@ -2237,10 +2006,10 @@
         <v>-1</v>
       </c>
       <c r="L20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N20">
         <v>-1</v>
@@ -2261,10 +2030,10 @@
         <v>-1</v>
       </c>
       <c r="T20">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U20">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V20">
         <v>6</v>
@@ -2302,10 +2071,10 @@
         <v>7</v>
       </c>
       <c r="H21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J21">
         <v>-1</v>
@@ -2314,10 +2083,10 @@
         <v>-1</v>
       </c>
       <c r="L21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N21">
         <v>-1</v>
@@ -2353,7 +2122,7 @@
         <v>9</v>
       </c>
       <c r="Y21">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="22" spans="1:25">
@@ -2379,10 +2148,10 @@
         <v>9</v>
       </c>
       <c r="H22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J22">
         <v>-1</v>
@@ -2391,10 +2160,10 @@
         <v>-1</v>
       </c>
       <c r="L22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N22">
         <v>-1</v>
@@ -2430,7 +2199,7 @@
         <v>10</v>
       </c>
       <c r="Y22">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="23" spans="1:25">
@@ -2456,10 +2225,10 @@
         <v>8</v>
       </c>
       <c r="H23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J23">
         <v>-1</v>
@@ -2468,10 +2237,10 @@
         <v>-1</v>
       </c>
       <c r="L23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N23">
         <v>-1</v>
@@ -2533,10 +2302,10 @@
         <v>10</v>
       </c>
       <c r="H24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J24">
         <v>-1</v>
@@ -2545,10 +2314,10 @@
         <v>-1</v>
       </c>
       <c r="L24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N24">
         <v>-1</v>
@@ -2610,10 +2379,10 @@
         <v>8</v>
       </c>
       <c r="H25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J25">
         <v>-1</v>
@@ -2622,10 +2391,10 @@
         <v>-1</v>
       </c>
       <c r="L25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N25">
         <v>-1</v>
@@ -2661,7 +2430,7 @@
         <v>9</v>
       </c>
       <c r="Y25">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="26" spans="1:25">
@@ -2687,10 +2456,10 @@
         <v>5</v>
       </c>
       <c r="H26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J26">
         <v>-1</v>
@@ -2699,10 +2468,10 @@
         <v>-1</v>
       </c>
       <c r="L26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N26">
         <v>-1</v>
@@ -2735,7 +2504,7 @@
         <v>7</v>
       </c>
       <c r="X26">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y26">
         <v>5</v>
@@ -2764,10 +2533,10 @@
         <v>7</v>
       </c>
       <c r="H27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J27">
         <v>-1</v>
@@ -2776,10 +2545,10 @@
         <v>-1</v>
       </c>
       <c r="L27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N27">
         <v>-1</v>
@@ -2800,10 +2569,10 @@
         <v>-1</v>
       </c>
       <c r="T27">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U27">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V27">
         <v>8</v>
@@ -2841,10 +2610,10 @@
         <v>8</v>
       </c>
       <c r="H28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J28">
         <v>-1</v>
@@ -2853,10 +2622,10 @@
         <v>-1</v>
       </c>
       <c r="L28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N28">
         <v>-1</v>
@@ -2877,10 +2646,10 @@
         <v>-1</v>
       </c>
       <c r="T28">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U28">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V28">
         <v>10</v>
@@ -2918,10 +2687,10 @@
         <v>5</v>
       </c>
       <c r="H29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J29">
         <v>-1</v>
@@ -2930,10 +2699,10 @@
         <v>-1</v>
       </c>
       <c r="L29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N29">
         <v>-1</v>
@@ -2966,10 +2735,10 @@
         <v>6</v>
       </c>
       <c r="X29">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y29">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="30" spans="1:25">
@@ -2995,10 +2764,10 @@
         <v>9</v>
       </c>
       <c r="H30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J30">
         <v>-1</v>
@@ -3007,10 +2776,10 @@
         <v>-1</v>
       </c>
       <c r="L30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N30">
         <v>-1</v>
@@ -3046,7 +2815,7 @@
         <v>10</v>
       </c>
       <c r="Y30">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="31" spans="1:25">
@@ -3072,10 +2841,10 @@
         <v>9</v>
       </c>
       <c r="H31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J31">
         <v>-1</v>
@@ -3084,10 +2853,10 @@
         <v>-1</v>
       </c>
       <c r="L31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N31">
         <v>-1</v>
@@ -3108,10 +2877,10 @@
         <v>-1</v>
       </c>
       <c r="T31">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U31">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V31">
         <v>10</v>
@@ -3123,7 +2892,7 @@
         <v>9</v>
       </c>
       <c r="Y31">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="32" spans="1:25">
@@ -3149,10 +2918,10 @@
         <v>7</v>
       </c>
       <c r="H32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J32">
         <v>-1</v>
@@ -3161,10 +2930,10 @@
         <v>-1</v>
       </c>
       <c r="L32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N32">
         <v>-1</v>
@@ -3185,10 +2954,10 @@
         <v>-1</v>
       </c>
       <c r="T32">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U32">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V32">
         <v>10</v>
@@ -3200,7 +2969,7 @@
         <v>9</v>
       </c>
       <c r="Y32">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="33" spans="1:25">
@@ -3226,10 +2995,10 @@
         <v>9</v>
       </c>
       <c r="H33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J33">
         <v>-1</v>
@@ -3238,10 +3007,10 @@
         <v>-1</v>
       </c>
       <c r="L33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N33">
         <v>-1</v>
@@ -3303,10 +3072,10 @@
         <v>7</v>
       </c>
       <c r="H34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J34">
         <v>-1</v>
@@ -3315,10 +3084,10 @@
         <v>-1</v>
       </c>
       <c r="L34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N34">
         <v>-1</v>
@@ -3354,7 +3123,7 @@
         <v>9</v>
       </c>
       <c r="Y34">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="35" spans="1:25">
@@ -3380,10 +3149,10 @@
         <v>10</v>
       </c>
       <c r="H35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J35">
         <v>-1</v>
@@ -3392,10 +3161,10 @@
         <v>-1</v>
       </c>
       <c r="L35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N35">
         <v>-1</v>
@@ -3416,10 +3185,10 @@
         <v>-1</v>
       </c>
       <c r="T35">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U35">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V35">
         <v>10</v>
@@ -3428,7 +3197,7 @@
         <v>8</v>
       </c>
       <c r="X35">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y35">
         <v>10</v>
@@ -3457,10 +3226,10 @@
         <v>10</v>
       </c>
       <c r="H36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J36">
         <v>-1</v>
@@ -3469,10 +3238,10 @@
         <v>-1</v>
       </c>
       <c r="L36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N36">
         <v>-1</v>
@@ -3505,7 +3274,7 @@
         <v>7</v>
       </c>
       <c r="X36">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y36">
         <v>10</v>
@@ -3534,10 +3303,10 @@
         <v>10</v>
       </c>
       <c r="H37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J37">
         <v>-1</v>
@@ -3546,10 +3315,10 @@
         <v>-1</v>
       </c>
       <c r="L37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N37">
         <v>-1</v>
@@ -3570,10 +3339,10 @@
         <v>-1</v>
       </c>
       <c r="T37">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U37">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V37">
         <v>10</v>
@@ -3721,10 +3490,10 @@
         <v>92</v>
       </c>
       <c r="H4">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="I4">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="J4">
         <v>0</v>
@@ -3733,10 +3502,10 @@
         <v>0</v>
       </c>
       <c r="L4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M4">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="N4">
         <v>0</v>
@@ -3780,10 +3549,10 @@
         <v>80</v>
       </c>
       <c r="H5">
-        <v>0</v>
+        <v>112.5</v>
       </c>
       <c r="I5">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="J5">
         <v>0</v>
@@ -3792,10 +3561,10 @@
         <v>0</v>
       </c>
       <c r="L5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M5">
-        <v>0</v>
+        <v>88</v>
       </c>
       <c r="N5">
         <v>0</v>
@@ -3839,10 +3608,10 @@
         <v>92</v>
       </c>
       <c r="H6">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="I6">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="J6">
         <v>0</v>
@@ -3851,10 +3620,10 @@
         <v>0</v>
       </c>
       <c r="L6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M6">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="N6">
         <v>0</v>
@@ -3898,10 +3667,10 @@
         <v>100</v>
       </c>
       <c r="H7">
-        <v>0</v>
+        <v>112.5</v>
       </c>
       <c r="I7">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="J7">
         <v>0</v>
@@ -3910,10 +3679,10 @@
         <v>0</v>
       </c>
       <c r="L7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M7">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="N7">
         <v>0</v>
@@ -3957,10 +3726,10 @@
         <v>100</v>
       </c>
       <c r="H8">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="I8">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="J8">
         <v>0</v>
@@ -3969,10 +3738,10 @@
         <v>0</v>
       </c>
       <c r="L8">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M8">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="N8">
         <v>0</v>
@@ -4016,10 +3785,10 @@
         <v>100</v>
       </c>
       <c r="H9">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="I9">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="J9">
         <v>0</v>
@@ -4028,10 +3797,10 @@
         <v>0</v>
       </c>
       <c r="L9">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="M9">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="N9">
         <v>0</v>
@@ -4075,10 +3844,10 @@
         <v>92</v>
       </c>
       <c r="H10">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="I10">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="J10">
         <v>0</v>
@@ -4087,10 +3856,10 @@
         <v>0</v>
       </c>
       <c r="L10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M10">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="N10">
         <v>0</v>
@@ -4134,10 +3903,10 @@
         <v>88</v>
       </c>
       <c r="H11">
-        <v>0</v>
+        <v>112.5</v>
       </c>
       <c r="I11">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="J11">
         <v>0</v>
@@ -4146,10 +3915,10 @@
         <v>0</v>
       </c>
       <c r="L11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M11">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="N11">
         <v>0</v>
@@ -4193,10 +3962,10 @@
         <v>100</v>
       </c>
       <c r="H12">
-        <v>0</v>
+        <v>115</v>
       </c>
       <c r="I12">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="J12">
         <v>0</v>
@@ -4205,10 +3974,10 @@
         <v>0</v>
       </c>
       <c r="L12">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M12">
-        <v>0</v>
+        <v>88</v>
       </c>
       <c r="N12">
         <v>0</v>
@@ -4252,10 +4021,10 @@
         <v>92</v>
       </c>
       <c r="H13">
-        <v>0</v>
+        <v>115</v>
       </c>
       <c r="I13">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="J13">
         <v>0</v>
@@ -4264,10 +4033,10 @@
         <v>0</v>
       </c>
       <c r="L13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M13">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="N13">
         <v>0</v>
@@ -4311,10 +4080,10 @@
         <v>100</v>
       </c>
       <c r="H14">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="I14">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="J14">
         <v>0</v>
@@ -4323,10 +4092,10 @@
         <v>0</v>
       </c>
       <c r="L14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M14">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="N14">
         <v>0</v>
@@ -4370,10 +4139,10 @@
         <v>100</v>
       </c>
       <c r="H15">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="I15">
-        <v>0</v>
+        <v>115</v>
       </c>
       <c r="J15">
         <v>0</v>
@@ -4382,10 +4151,10 @@
         <v>0</v>
       </c>
       <c r="L15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M15">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="N15">
         <v>0</v>
@@ -4429,10 +4198,10 @@
         <v>100</v>
       </c>
       <c r="H16">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="I16">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="J16">
         <v>0</v>
@@ -4441,10 +4210,10 @@
         <v>0</v>
       </c>
       <c r="L16">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M16">
-        <v>0</v>
+        <v>88</v>
       </c>
       <c r="N16">
         <v>0</v>
@@ -4488,10 +4257,10 @@
         <v>80</v>
       </c>
       <c r="H17">
-        <v>0</v>
+        <v>112.5</v>
       </c>
       <c r="I17">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="J17">
         <v>0</v>
@@ -4500,10 +4269,10 @@
         <v>0</v>
       </c>
       <c r="L17">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M17">
-        <v>0</v>
+        <v>88</v>
       </c>
       <c r="N17">
         <v>0</v>
@@ -4547,10 +4316,10 @@
         <v>100</v>
       </c>
       <c r="H18">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="I18">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="J18">
         <v>0</v>
@@ -4559,10 +4328,10 @@
         <v>0</v>
       </c>
       <c r="L18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M18">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="N18">
         <v>0</v>
@@ -4606,10 +4375,10 @@
         <v>92</v>
       </c>
       <c r="H19">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="I19">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="J19">
         <v>0</v>
@@ -4618,10 +4387,10 @@
         <v>0</v>
       </c>
       <c r="L19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M19">
-        <v>0</v>
+        <v>88</v>
       </c>
       <c r="N19">
         <v>0</v>
@@ -4665,10 +4434,10 @@
         <v>88</v>
       </c>
       <c r="H20">
-        <v>0</v>
+        <v>112.5</v>
       </c>
       <c r="I20">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="J20">
         <v>0</v>
@@ -4677,10 +4446,10 @@
         <v>0</v>
       </c>
       <c r="L20">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M20">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="N20">
         <v>0</v>
@@ -4724,10 +4493,10 @@
         <v>100</v>
       </c>
       <c r="H21">
-        <v>0</v>
+        <v>115</v>
       </c>
       <c r="I21">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="J21">
         <v>0</v>
@@ -4736,10 +4505,10 @@
         <v>0</v>
       </c>
       <c r="L21">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M21">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="N21">
         <v>0</v>
@@ -4783,10 +4552,10 @@
         <v>100</v>
       </c>
       <c r="H22">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="I22">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="J22">
         <v>0</v>
@@ -4795,10 +4564,10 @@
         <v>0</v>
       </c>
       <c r="L22">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M22">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="N22">
         <v>0</v>
@@ -4842,10 +4611,10 @@
         <v>88</v>
       </c>
       <c r="H23">
-        <v>0</v>
+        <v>115</v>
       </c>
       <c r="I23">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="J23">
         <v>0</v>
@@ -4854,10 +4623,10 @@
         <v>0</v>
       </c>
       <c r="L23">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M23">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="N23">
         <v>0</v>
@@ -4901,10 +4670,10 @@
         <v>100</v>
       </c>
       <c r="H24">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="I24">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="J24">
         <v>0</v>
@@ -4913,10 +4682,10 @@
         <v>0</v>
       </c>
       <c r="L24">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M24">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="N24">
         <v>0</v>
@@ -4960,10 +4729,10 @@
         <v>100</v>
       </c>
       <c r="H25">
-        <v>0</v>
+        <v>117.5</v>
       </c>
       <c r="I25">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="J25">
         <v>0</v>
@@ -4972,10 +4741,10 @@
         <v>0</v>
       </c>
       <c r="L25">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M25">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="N25">
         <v>0</v>
@@ -5019,10 +4788,10 @@
         <v>80</v>
       </c>
       <c r="H26">
-        <v>0</v>
+        <v>112.5</v>
       </c>
       <c r="I26">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="J26">
         <v>0</v>
@@ -5031,10 +4800,10 @@
         <v>0</v>
       </c>
       <c r="L26">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M26">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="N26">
         <v>0</v>
@@ -5078,10 +4847,10 @@
         <v>80</v>
       </c>
       <c r="H27">
-        <v>0</v>
+        <v>112.5</v>
       </c>
       <c r="I27">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="J27">
         <v>0</v>
@@ -5090,10 +4859,10 @@
         <v>0</v>
       </c>
       <c r="L27">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M27">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="N27">
         <v>0</v>
@@ -5137,10 +4906,10 @@
         <v>84</v>
       </c>
       <c r="H28">
-        <v>0</v>
+        <v>115</v>
       </c>
       <c r="I28">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="J28">
         <v>0</v>
@@ -5149,10 +4918,10 @@
         <v>0</v>
       </c>
       <c r="L28">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M28">
-        <v>0</v>
+        <v>88</v>
       </c>
       <c r="N28">
         <v>0</v>
@@ -5196,10 +4965,10 @@
         <v>84</v>
       </c>
       <c r="H29">
-        <v>0</v>
+        <v>112.5</v>
       </c>
       <c r="I29">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="J29">
         <v>0</v>
@@ -5208,10 +4977,10 @@
         <v>0</v>
       </c>
       <c r="L29">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M29">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="N29">
         <v>0</v>
@@ -5255,10 +5024,10 @@
         <v>100</v>
       </c>
       <c r="H30">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="I30">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="J30">
         <v>0</v>
@@ -5267,10 +5036,10 @@
         <v>0</v>
       </c>
       <c r="L30">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M30">
-        <v>0</v>
+        <v>88</v>
       </c>
       <c r="N30">
         <v>0</v>
@@ -5314,10 +5083,10 @@
         <v>100</v>
       </c>
       <c r="H31">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="I31">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="J31">
         <v>0</v>
@@ -5326,10 +5095,10 @@
         <v>0</v>
       </c>
       <c r="L31">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M31">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="N31">
         <v>0</v>
@@ -5373,10 +5142,10 @@
         <v>100</v>
       </c>
       <c r="H32">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="I32">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="J32">
         <v>0</v>
@@ -5385,10 +5154,10 @@
         <v>0</v>
       </c>
       <c r="L32">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M32">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="N32">
         <v>0</v>
@@ -5432,10 +5201,10 @@
         <v>100</v>
       </c>
       <c r="H33">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="I33">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="J33">
         <v>0</v>
@@ -5444,10 +5213,10 @@
         <v>0</v>
       </c>
       <c r="L33">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M33">
-        <v>0</v>
+        <v>88</v>
       </c>
       <c r="N33">
         <v>0</v>
@@ -5491,10 +5260,10 @@
         <v>100</v>
       </c>
       <c r="H34">
-        <v>0</v>
+        <v>112.5</v>
       </c>
       <c r="I34">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="J34">
         <v>0</v>
@@ -5503,10 +5272,10 @@
         <v>0</v>
       </c>
       <c r="L34">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M34">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="N34">
         <v>0</v>
@@ -5550,10 +5319,10 @@
         <v>100</v>
       </c>
       <c r="H35">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="I35">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="J35">
         <v>0</v>
@@ -5562,10 +5331,10 @@
         <v>0</v>
       </c>
       <c r="L35">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M35">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="N35">
         <v>0</v>
@@ -5609,10 +5378,10 @@
         <v>100</v>
       </c>
       <c r="H36">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="I36">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="J36">
         <v>0</v>
@@ -5621,10 +5390,10 @@
         <v>0</v>
       </c>
       <c r="L36">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M36">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="N36">
         <v>0</v>
@@ -5668,10 +5437,10 @@
         <v>100</v>
       </c>
       <c r="H37">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="I37">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="J37">
         <v>0</v>
@@ -5680,10 +5449,10 @@
         <v>0</v>
       </c>
       <c r="L37">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M37">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="N37">
         <v>0</v>
@@ -5720,6 +5489,8 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="50.7109375" customWidth="1"/>
+    <col min="6" max="7" width="9.140625" style="2"/>
+    <col min="10" max="10" width="9.140625" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10">
@@ -5770,11 +5541,11 @@
       <c r="E2">
         <v>3</v>
       </c>
-      <c r="F2">
-        <v>91.18000000000001</v>
-      </c>
-      <c r="G2">
-        <v>8.82</v>
+      <c r="F2" s="2">
+        <v>91.2</v>
+      </c>
+      <c r="G2" s="2">
+        <v>8.800000000000001</v>
       </c>
       <c r="H2">
         <v>7.6</v>
@@ -5782,7 +5553,7 @@
       <c r="I2">
         <v>0</v>
       </c>
-      <c r="J2">
+      <c r="J2" s="2">
         <v>0</v>
       </c>
     </row>
@@ -5797,24 +5568,24 @@
         <v>34</v>
       </c>
       <c r="D3">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E3">
-        <v>2</v>
-      </c>
-      <c r="F3">
-        <v>94.12</v>
-      </c>
-      <c r="G3">
-        <v>5.88</v>
+        <v>1</v>
+      </c>
+      <c r="F3" s="2">
+        <v>97.09999999999999</v>
+      </c>
+      <c r="G3" s="2">
+        <v>2.9</v>
       </c>
       <c r="H3">
-        <v>8.1</v>
+        <v>8.5</v>
       </c>
       <c r="I3">
         <v>0</v>
       </c>
-      <c r="J3">
+      <c r="J3" s="2">
         <v>0</v>
       </c>
     </row>
@@ -5829,16 +5600,16 @@
         <v>34</v>
       </c>
       <c r="D4">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E4">
-        <v>1</v>
-      </c>
-      <c r="F4">
-        <v>97.06</v>
-      </c>
-      <c r="G4">
-        <v>2.94</v>
+        <v>0</v>
+      </c>
+      <c r="F4" s="2">
+        <v>100</v>
+      </c>
+      <c r="G4" s="2">
+        <v>0</v>
       </c>
       <c r="H4">
         <v>9</v>
@@ -5846,7 +5617,7 @@
       <c r="I4">
         <v>0</v>
       </c>
-      <c r="J4">
+      <c r="J4" s="2">
         <v>0</v>
       </c>
     </row>
@@ -5866,10 +5637,10 @@
       <c r="E5">
         <v>0</v>
       </c>
-      <c r="F5">
-        <v>100</v>
-      </c>
-      <c r="G5">
+      <c r="F5" s="2">
+        <v>100</v>
+      </c>
+      <c r="G5" s="2">
         <v>0</v>
       </c>
       <c r="H5">
@@ -5878,7 +5649,7 @@
       <c r="I5">
         <v>0</v>
       </c>
-      <c r="J5">
+      <c r="J5" s="2">
         <v>0</v>
       </c>
     </row>
@@ -5898,19 +5669,19 @@
       <c r="E6">
         <v>0</v>
       </c>
-      <c r="F6">
-        <v>100</v>
-      </c>
-      <c r="G6">
+      <c r="F6" s="2">
+        <v>100</v>
+      </c>
+      <c r="G6" s="2">
         <v>0</v>
       </c>
       <c r="H6">
-        <v>9</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="I6">
         <v>0</v>
       </c>
-      <c r="J6">
+      <c r="J6" s="2">
         <v>0</v>
       </c>
     </row>
@@ -5930,19 +5701,19 @@
       <c r="E7">
         <v>0</v>
       </c>
-      <c r="F7">
-        <v>100</v>
-      </c>
-      <c r="G7">
+      <c r="F7" s="2">
+        <v>100</v>
+      </c>
+      <c r="G7" s="2">
         <v>0</v>
       </c>
       <c r="H7">
-        <v>9</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="I7">
         <v>0</v>
       </c>
-      <c r="J7">
+      <c r="J7" s="2">
         <v>0</v>
       </c>
     </row>
@@ -5987,616 +5758,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E35"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="30.7109375" customWidth="1"/>
-    <col min="2" max="4" width="50.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2">
-        <v>20330051920187</v>
-      </c>
-      <c r="B2" t="s">
-        <v>67</v>
-      </c>
-      <c r="C2" t="s">
-        <v>96</v>
-      </c>
-      <c r="D2" t="s">
-        <v>123</v>
-      </c>
-      <c r="E2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
-      <c r="A3">
-        <v>20330051920220</v>
-      </c>
-      <c r="B3" t="s">
-        <v>68</v>
-      </c>
-      <c r="C3" t="s">
-        <v>77</v>
-      </c>
-      <c r="D3" t="s">
-        <v>124</v>
-      </c>
-      <c r="E3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
-      <c r="A4">
-        <v>20330051920221</v>
-      </c>
-      <c r="B4" t="s">
-        <v>69</v>
-      </c>
-      <c r="C4" t="s">
-        <v>97</v>
-      </c>
-      <c r="D4" t="s">
-        <v>125</v>
-      </c>
-      <c r="E4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5">
-      <c r="A5">
-        <v>20330051920374</v>
-      </c>
-      <c r="B5" t="s">
-        <v>70</v>
-      </c>
-      <c r="C5" t="s">
-        <v>98</v>
-      </c>
-      <c r="D5" t="s">
-        <v>126</v>
-      </c>
-      <c r="E5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5">
-      <c r="A6">
-        <v>20330051920223</v>
-      </c>
-      <c r="B6" t="s">
-        <v>71</v>
-      </c>
-      <c r="C6" t="s">
-        <v>99</v>
-      </c>
-      <c r="D6" t="s">
-        <v>127</v>
-      </c>
-      <c r="E6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5">
-      <c r="A7">
-        <v>20330051920224</v>
-      </c>
-      <c r="B7" t="s">
-        <v>72</v>
-      </c>
-      <c r="C7" t="s">
-        <v>100</v>
-      </c>
-      <c r="D7" t="s">
-        <v>128</v>
-      </c>
-      <c r="E7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5">
-      <c r="A8">
-        <v>20330051920225</v>
-      </c>
-      <c r="B8" t="s">
-        <v>73</v>
-      </c>
-      <c r="C8" t="s">
-        <v>101</v>
-      </c>
-      <c r="D8" t="s">
-        <v>129</v>
-      </c>
-      <c r="E8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5">
-      <c r="A9">
-        <v>20330051920375</v>
-      </c>
-      <c r="B9" t="s">
-        <v>74</v>
-      </c>
-      <c r="C9" t="s">
-        <v>102</v>
-      </c>
-      <c r="D9" t="s">
-        <v>130</v>
-      </c>
-      <c r="E9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5">
-      <c r="A10">
-        <v>20330051920226</v>
-      </c>
-      <c r="B10" t="s">
-        <v>75</v>
-      </c>
-      <c r="C10" t="s">
-        <v>73</v>
-      </c>
-      <c r="D10" t="s">
-        <v>131</v>
-      </c>
-      <c r="E10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5">
-      <c r="A11">
-        <v>20330051920227</v>
-      </c>
-      <c r="B11" t="s">
-        <v>76</v>
-      </c>
-      <c r="C11" t="s">
-        <v>103</v>
-      </c>
-      <c r="D11" t="s">
-        <v>132</v>
-      </c>
-      <c r="E11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5">
-      <c r="A12">
-        <v>20330051920228</v>
-      </c>
-      <c r="B12" t="s">
-        <v>77</v>
-      </c>
-      <c r="C12" t="s">
-        <v>104</v>
-      </c>
-      <c r="D12" t="s">
-        <v>133</v>
-      </c>
-      <c r="E12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5">
-      <c r="A13">
-        <v>20330051920229</v>
-      </c>
-      <c r="B13" t="s">
-        <v>77</v>
-      </c>
-      <c r="C13" t="s">
-        <v>105</v>
-      </c>
-      <c r="D13" t="s">
-        <v>134</v>
-      </c>
-      <c r="E13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5">
-      <c r="A14">
-        <v>20330051920230</v>
-      </c>
-      <c r="B14" t="s">
-        <v>77</v>
-      </c>
-      <c r="C14" t="s">
-        <v>106</v>
-      </c>
-      <c r="D14" t="s">
-        <v>135</v>
-      </c>
-      <c r="E14">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5">
-      <c r="A15">
-        <v>20330051920231</v>
-      </c>
-      <c r="B15" t="s">
-        <v>78</v>
-      </c>
-      <c r="C15" t="s">
-        <v>107</v>
-      </c>
-      <c r="D15" t="s">
-        <v>136</v>
-      </c>
-      <c r="E15">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5">
-      <c r="A16">
-        <v>20330051920232</v>
-      </c>
-      <c r="B16" t="s">
-        <v>79</v>
-      </c>
-      <c r="C16" t="s">
-        <v>108</v>
-      </c>
-      <c r="D16" t="s">
-        <v>137</v>
-      </c>
-      <c r="E16">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17">
-        <v>20330051920233</v>
-      </c>
-      <c r="B17" t="s">
-        <v>80</v>
-      </c>
-      <c r="C17" t="s">
-        <v>109</v>
-      </c>
-      <c r="D17" t="s">
-        <v>138</v>
-      </c>
-      <c r="E17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18">
-        <v>20330051920234</v>
-      </c>
-      <c r="B18" t="s">
-        <v>81</v>
-      </c>
-      <c r="C18" t="s">
-        <v>110</v>
-      </c>
-      <c r="D18" t="s">
-        <v>139</v>
-      </c>
-      <c r="E18">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19">
-        <v>20330051920376</v>
-      </c>
-      <c r="B19" t="s">
-        <v>82</v>
-      </c>
-      <c r="C19" t="s">
-        <v>111</v>
-      </c>
-      <c r="D19" t="s">
-        <v>140</v>
-      </c>
-      <c r="E19">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20">
-        <v>20330051920236</v>
-      </c>
-      <c r="B20" t="s">
-        <v>83</v>
-      </c>
-      <c r="C20" t="s">
-        <v>112</v>
-      </c>
-      <c r="D20" t="s">
-        <v>141</v>
-      </c>
-      <c r="E20">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21">
-        <v>20330051920238</v>
-      </c>
-      <c r="B21" t="s">
-        <v>84</v>
-      </c>
-      <c r="C21" t="s">
-        <v>113</v>
-      </c>
-      <c r="D21" t="s">
-        <v>142</v>
-      </c>
-      <c r="E21">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22">
-        <v>20330051920239</v>
-      </c>
-      <c r="B22" t="s">
-        <v>85</v>
-      </c>
-      <c r="C22" t="s">
-        <v>72</v>
-      </c>
-      <c r="D22" t="s">
-        <v>143</v>
-      </c>
-      <c r="E22">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23">
-        <v>20330051920240</v>
-      </c>
-      <c r="B23" t="s">
-        <v>84</v>
-      </c>
-      <c r="C23" t="s">
-        <v>114</v>
-      </c>
-      <c r="D23" t="s">
-        <v>144</v>
-      </c>
-      <c r="E23">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24">
-        <v>20330051920241</v>
-      </c>
-      <c r="B24" t="s">
-        <v>86</v>
-      </c>
-      <c r="C24" t="s">
-        <v>115</v>
-      </c>
-      <c r="D24" t="s">
-        <v>145</v>
-      </c>
-      <c r="E24">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25">
-        <v>20330051920243</v>
-      </c>
-      <c r="B25" t="s">
-        <v>87</v>
-      </c>
-      <c r="C25" t="s">
-        <v>75</v>
-      </c>
-      <c r="D25" t="s">
-        <v>146</v>
-      </c>
-      <c r="E25">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26">
-        <v>20330051920244</v>
-      </c>
-      <c r="B26" t="s">
-        <v>88</v>
-      </c>
-      <c r="C26" t="s">
-        <v>108</v>
-      </c>
-      <c r="D26" t="s">
-        <v>147</v>
-      </c>
-      <c r="E26">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27">
-        <v>20330051920248</v>
-      </c>
-      <c r="B27" t="s">
-        <v>89</v>
-      </c>
-      <c r="C27" t="s">
-        <v>78</v>
-      </c>
-      <c r="D27" t="s">
-        <v>148</v>
-      </c>
-      <c r="E27">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28">
-        <v>20330051920249</v>
-      </c>
-      <c r="B28" t="s">
-        <v>89</v>
-      </c>
-      <c r="C28" t="s">
-        <v>116</v>
-      </c>
-      <c r="D28" t="s">
-        <v>149</v>
-      </c>
-      <c r="E28">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29">
-        <v>20330051920250</v>
-      </c>
-      <c r="B29" t="s">
-        <v>90</v>
-      </c>
-      <c r="C29" t="s">
-        <v>117</v>
-      </c>
-      <c r="D29" t="s">
-        <v>150</v>
-      </c>
-      <c r="E29">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30">
-        <v>20330051920251</v>
-      </c>
-      <c r="B30" t="s">
-        <v>91</v>
-      </c>
-      <c r="C30" t="s">
-        <v>118</v>
-      </c>
-      <c r="D30" t="s">
-        <v>151</v>
-      </c>
-      <c r="E30">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31">
-        <v>20330051920252</v>
-      </c>
-      <c r="B31" t="s">
-        <v>92</v>
-      </c>
-      <c r="C31" t="s">
-        <v>119</v>
-      </c>
-      <c r="D31" t="s">
-        <v>152</v>
-      </c>
-      <c r="E31">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32">
-        <v>20330051920253</v>
-      </c>
-      <c r="B32" t="s">
-        <v>92</v>
-      </c>
-      <c r="C32" t="s">
-        <v>120</v>
-      </c>
-      <c r="D32" t="s">
-        <v>153</v>
-      </c>
-      <c r="E32">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33">
-        <v>20330051920256</v>
-      </c>
-      <c r="B33" t="s">
-        <v>93</v>
-      </c>
-      <c r="C33" t="s">
-        <v>121</v>
-      </c>
-      <c r="D33" t="s">
-        <v>154</v>
-      </c>
-      <c r="E33">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34">
-        <v>20330051920257</v>
-      </c>
-      <c r="B34" t="s">
-        <v>94</v>
-      </c>
-      <c r="C34" t="s">
-        <v>122</v>
-      </c>
-      <c r="D34" t="s">
-        <v>155</v>
-      </c>
-      <c r="E34">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35">
-        <v>20330051920258</v>
-      </c>
-      <c r="B35" t="s">
-        <v>95</v>
-      </c>
-      <c r="C35" t="s">
-        <v>95</v>
-      </c>
-      <c r="D35" t="s">
-        <v>156</v>
-      </c>
-      <c r="E35">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -6628,22 +5790,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>20330051920236</v>
+        <v>20330051920226</v>
       </c>
       <c r="B2" t="s">
-        <v>83</v>
+        <v>67</v>
       </c>
       <c r="C2" t="s">
-        <v>112</v>
+        <v>71</v>
       </c>
       <c r="D2" t="s">
-        <v>141</v>
+        <v>75</v>
       </c>
       <c r="E2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -6654,13 +5816,13 @@
         <v>20330051920236</v>
       </c>
       <c r="B3" t="s">
-        <v>83</v>
+        <v>68</v>
       </c>
       <c r="C3" t="s">
-        <v>112</v>
+        <v>72</v>
       </c>
       <c r="D3" t="s">
-        <v>141</v>
+        <v>76</v>
       </c>
       <c r="E3" t="s">
         <v>10</v>
@@ -6674,16 +5836,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>20330051920226</v>
+        <v>20330051920240</v>
       </c>
       <c r="B4" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="C4" t="s">
         <v>73</v>
       </c>
       <c r="D4" t="s">
-        <v>131</v>
+        <v>77</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -6697,16 +5859,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>20330051920240</v>
+        <v>20330051920251</v>
       </c>
       <c r="B5" t="s">
-        <v>84</v>
+        <v>70</v>
       </c>
       <c r="C5" t="s">
-        <v>114</v>
+        <v>74</v>
       </c>
       <c r="D5" t="s">
-        <v>144</v>
+        <v>78</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -6715,52 +5877,6 @@
         <v>58</v>
       </c>
       <c r="G5">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6">
-        <v>20330051920244</v>
-      </c>
-      <c r="B6" t="s">
-        <v>88</v>
-      </c>
-      <c r="C6" t="s">
-        <v>108</v>
-      </c>
-      <c r="D6" t="s">
-        <v>147</v>
-      </c>
-      <c r="E6" t="s">
-        <v>10</v>
-      </c>
-      <c r="F6" t="s">
-        <v>59</v>
-      </c>
-      <c r="G6">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>20330051920251</v>
-      </c>
-      <c r="B7" t="s">
-        <v>91</v>
-      </c>
-      <c r="C7" t="s">
-        <v>118</v>
-      </c>
-      <c r="D7" t="s">
-        <v>151</v>
-      </c>
-      <c r="E7" t="s">
-        <v>8</v>
-      </c>
-      <c r="F7" t="s">
-        <v>58</v>
-      </c>
-      <c r="G7">
         <v>5</v>
       </c>
     </row>

--- a/grupos/6ALCM - Estadisticos 20222.xlsx
+++ b/grupos/6ALCM - Estadisticos 20222.xlsx
@@ -768,7 +768,7 @@
         <v>10</v>
       </c>
       <c r="J4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K4">
         <v>-1</v>
@@ -804,7 +804,7 @@
         <v>10</v>
       </c>
       <c r="V4">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W4">
         <v>9</v>
@@ -845,7 +845,7 @@
         <v>9</v>
       </c>
       <c r="J5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K5">
         <v>-1</v>
@@ -922,7 +922,7 @@
         <v>10</v>
       </c>
       <c r="J6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K6">
         <v>-1</v>
@@ -999,7 +999,7 @@
         <v>10</v>
       </c>
       <c r="J7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K7">
         <v>-1</v>
@@ -1076,7 +1076,7 @@
         <v>9</v>
       </c>
       <c r="J8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K8">
         <v>-1</v>
@@ -1153,7 +1153,7 @@
         <v>10</v>
       </c>
       <c r="J9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K9">
         <v>-1</v>
@@ -1230,7 +1230,7 @@
         <v>10</v>
       </c>
       <c r="J10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K10">
         <v>-1</v>
@@ -1307,7 +1307,7 @@
         <v>7</v>
       </c>
       <c r="J11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K11">
         <v>-1</v>
@@ -1343,7 +1343,7 @@
         <v>7</v>
       </c>
       <c r="V11">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="W11">
         <v>5</v>
@@ -1384,7 +1384,7 @@
         <v>9</v>
       </c>
       <c r="J12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K12">
         <v>-1</v>
@@ -1461,7 +1461,7 @@
         <v>9</v>
       </c>
       <c r="J13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K13">
         <v>-1</v>
@@ -1497,7 +1497,7 @@
         <v>9</v>
       </c>
       <c r="V13">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W13">
         <v>5</v>
@@ -1538,7 +1538,7 @@
         <v>10</v>
       </c>
       <c r="J14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K14">
         <v>-1</v>
@@ -1574,7 +1574,7 @@
         <v>10</v>
       </c>
       <c r="V14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W14">
         <v>10</v>
@@ -1615,7 +1615,7 @@
         <v>9</v>
       </c>
       <c r="J15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K15">
         <v>-1</v>
@@ -1651,7 +1651,7 @@
         <v>9</v>
       </c>
       <c r="V15">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W15">
         <v>7</v>
@@ -1692,7 +1692,7 @@
         <v>10</v>
       </c>
       <c r="J16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K16">
         <v>-1</v>
@@ -1769,7 +1769,7 @@
         <v>9</v>
       </c>
       <c r="J17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K17">
         <v>-1</v>
@@ -1846,7 +1846,7 @@
         <v>9</v>
       </c>
       <c r="J18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K18">
         <v>-1</v>
@@ -1882,7 +1882,7 @@
         <v>9</v>
       </c>
       <c r="V18">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W18">
         <v>7</v>
@@ -1923,7 +1923,7 @@
         <v>9</v>
       </c>
       <c r="J19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K19">
         <v>-1</v>
@@ -1959,7 +1959,7 @@
         <v>10</v>
       </c>
       <c r="V19">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W19">
         <v>9</v>
@@ -2000,7 +2000,7 @@
         <v>9</v>
       </c>
       <c r="J20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K20">
         <v>-1</v>
@@ -2036,7 +2036,7 @@
         <v>8</v>
       </c>
       <c r="V20">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W20">
         <v>7</v>
@@ -2077,7 +2077,7 @@
         <v>9</v>
       </c>
       <c r="J21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K21">
         <v>-1</v>
@@ -2154,7 +2154,7 @@
         <v>10</v>
       </c>
       <c r="J22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K22">
         <v>-1</v>
@@ -2231,7 +2231,7 @@
         <v>9</v>
       </c>
       <c r="J23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K23">
         <v>-1</v>
@@ -2308,7 +2308,7 @@
         <v>10</v>
       </c>
       <c r="J24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K24">
         <v>-1</v>
@@ -2385,7 +2385,7 @@
         <v>9</v>
       </c>
       <c r="J25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K25">
         <v>-1</v>
@@ -2462,7 +2462,7 @@
         <v>8</v>
       </c>
       <c r="J26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K26">
         <v>-1</v>
@@ -2498,7 +2498,7 @@
         <v>9</v>
       </c>
       <c r="V26">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W26">
         <v>7</v>
@@ -2539,7 +2539,7 @@
         <v>9</v>
       </c>
       <c r="J27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K27">
         <v>-1</v>
@@ -2616,7 +2616,7 @@
         <v>8</v>
       </c>
       <c r="J28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K28">
         <v>-1</v>
@@ -2652,7 +2652,7 @@
         <v>8</v>
       </c>
       <c r="V28">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W28">
         <v>9</v>
@@ -2693,7 +2693,7 @@
         <v>8</v>
       </c>
       <c r="J29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K29">
         <v>-1</v>
@@ -2729,7 +2729,7 @@
         <v>8</v>
       </c>
       <c r="V29">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W29">
         <v>6</v>
@@ -2770,7 +2770,7 @@
         <v>10</v>
       </c>
       <c r="J30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K30">
         <v>-1</v>
@@ -2847,7 +2847,7 @@
         <v>10</v>
       </c>
       <c r="J31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K31">
         <v>-1</v>
@@ -2924,7 +2924,7 @@
         <v>9</v>
       </c>
       <c r="J32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K32">
         <v>-1</v>
@@ -3001,7 +3001,7 @@
         <v>10</v>
       </c>
       <c r="J33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K33">
         <v>-1</v>
@@ -3078,7 +3078,7 @@
         <v>9</v>
       </c>
       <c r="J34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K34">
         <v>-1</v>
@@ -3155,7 +3155,7 @@
         <v>10</v>
       </c>
       <c r="J35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K35">
         <v>-1</v>
@@ -3232,7 +3232,7 @@
         <v>10</v>
       </c>
       <c r="J36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K36">
         <v>-1</v>
@@ -3309,7 +3309,7 @@
         <v>10</v>
       </c>
       <c r="J37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K37">
         <v>-1</v>
@@ -3496,7 +3496,7 @@
         <v>120</v>
       </c>
       <c r="J4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K4">
         <v>0</v>
@@ -3555,7 +3555,7 @@
         <v>110</v>
       </c>
       <c r="J5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K5">
         <v>0</v>
@@ -3614,7 +3614,7 @@
         <v>120</v>
       </c>
       <c r="J6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K6">
         <v>0</v>
@@ -3673,7 +3673,7 @@
         <v>110</v>
       </c>
       <c r="J7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K7">
         <v>0</v>
@@ -3732,7 +3732,7 @@
         <v>120</v>
       </c>
       <c r="J8">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K8">
         <v>0</v>
@@ -3791,7 +3791,7 @@
         <v>120</v>
       </c>
       <c r="J9">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K9">
         <v>0</v>
@@ -3850,7 +3850,7 @@
         <v>120</v>
       </c>
       <c r="J10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K10">
         <v>0</v>
@@ -3909,7 +3909,7 @@
         <v>110</v>
       </c>
       <c r="J11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K11">
         <v>0</v>
@@ -3968,7 +3968,7 @@
         <v>120</v>
       </c>
       <c r="J12">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K12">
         <v>0</v>
@@ -4027,7 +4027,7 @@
         <v>120</v>
       </c>
       <c r="J13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K13">
         <v>0</v>
@@ -4086,7 +4086,7 @@
         <v>120</v>
       </c>
       <c r="J14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K14">
         <v>0</v>
@@ -4145,7 +4145,7 @@
         <v>115</v>
       </c>
       <c r="J15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K15">
         <v>0</v>
@@ -4204,7 +4204,7 @@
         <v>120</v>
       </c>
       <c r="J16">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K16">
         <v>0</v>
@@ -4263,7 +4263,7 @@
         <v>110</v>
       </c>
       <c r="J17">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K17">
         <v>0</v>
@@ -4322,7 +4322,7 @@
         <v>120</v>
       </c>
       <c r="J18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K18">
         <v>0</v>
@@ -4381,7 +4381,7 @@
         <v>120</v>
       </c>
       <c r="J19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K19">
         <v>0</v>
@@ -4440,7 +4440,7 @@
         <v>110</v>
       </c>
       <c r="J20">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K20">
         <v>0</v>
@@ -4499,7 +4499,7 @@
         <v>110</v>
       </c>
       <c r="J21">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K21">
         <v>0</v>
@@ -4558,7 +4558,7 @@
         <v>120</v>
       </c>
       <c r="J22">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K22">
         <v>0</v>
@@ -4617,7 +4617,7 @@
         <v>120</v>
       </c>
       <c r="J23">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K23">
         <v>0</v>
@@ -4676,7 +4676,7 @@
         <v>120</v>
       </c>
       <c r="J24">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K24">
         <v>0</v>
@@ -4735,7 +4735,7 @@
         <v>120</v>
       </c>
       <c r="J25">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K25">
         <v>0</v>
@@ -4794,7 +4794,7 @@
         <v>110</v>
       </c>
       <c r="J26">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K26">
         <v>0</v>
@@ -4853,7 +4853,7 @@
         <v>110</v>
       </c>
       <c r="J27">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K27">
         <v>0</v>
@@ -4912,7 +4912,7 @@
         <v>120</v>
       </c>
       <c r="J28">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K28">
         <v>0</v>
@@ -4971,7 +4971,7 @@
         <v>110</v>
       </c>
       <c r="J29">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K29">
         <v>0</v>
@@ -5030,7 +5030,7 @@
         <v>120</v>
       </c>
       <c r="J30">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K30">
         <v>0</v>
@@ -5089,7 +5089,7 @@
         <v>120</v>
       </c>
       <c r="J31">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K31">
         <v>0</v>
@@ -5148,7 +5148,7 @@
         <v>120</v>
       </c>
       <c r="J32">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K32">
         <v>0</v>
@@ -5207,7 +5207,7 @@
         <v>120</v>
       </c>
       <c r="J33">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K33">
         <v>0</v>
@@ -5266,7 +5266,7 @@
         <v>110</v>
       </c>
       <c r="J34">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K34">
         <v>0</v>
@@ -5325,7 +5325,7 @@
         <v>120</v>
       </c>
       <c r="J35">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K35">
         <v>0</v>
@@ -5384,7 +5384,7 @@
         <v>120</v>
       </c>
       <c r="J36">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K36">
         <v>0</v>
@@ -5443,7 +5443,7 @@
         <v>120</v>
       </c>
       <c r="J37">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K37">
         <v>0</v>
@@ -5644,7 +5644,7 @@
         <v>0</v>
       </c>
       <c r="H5">
-        <v>9.300000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="I5">
         <v>0</v>

--- a/grupos/6ALCM - Estadisticos 20222.xlsx
+++ b/grupos/6ALCM - Estadisticos 20222.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="70">
   <si>
     <t>Materia</t>
   </si>
@@ -194,12 +194,12 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>Ochoa Martínez Mayeli</t>
+  </si>
+  <si>
     <t>Velasco Sánchez David</t>
   </si>
   <si>
-    <t>Ochoa Martínez Mayeli</t>
-  </si>
-  <si>
     <t>Rivera Cruz Ezequiel</t>
   </si>
   <si>
@@ -221,40 +221,13 @@
     <t>Nombres</t>
   </si>
   <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
     <t>MAZAHUA</t>
   </si>
   <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>DE LOS SANTOS</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
     <t>ACEVEDO</t>
   </si>
   <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>CALIHUA</t>
-  </si>
-  <si>
-    <t>JESSICA</t>
-  </si>
-  <si>
     <t>GENARO RAFAEL</t>
-  </si>
-  <si>
-    <t>DIEGO</t>
-  </si>
-  <si>
-    <t>ANGEL EMMANUEL</t>
   </si>
 </sst>
 </file>
@@ -771,7 +744,7 @@
         <v>10</v>
       </c>
       <c r="K4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L4">
         <v>10</v>
@@ -807,7 +780,7 @@
         <v>10</v>
       </c>
       <c r="W4">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X4">
         <v>10</v>
@@ -848,7 +821,7 @@
         <v>9</v>
       </c>
       <c r="K5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L5">
         <v>9</v>
@@ -884,7 +857,7 @@
         <v>9</v>
       </c>
       <c r="W5">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X5">
         <v>9</v>
@@ -925,7 +898,7 @@
         <v>8</v>
       </c>
       <c r="K6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L6">
         <v>7</v>
@@ -961,7 +934,7 @@
         <v>9</v>
       </c>
       <c r="W6">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X6">
         <v>8</v>
@@ -1002,7 +975,7 @@
         <v>10</v>
       </c>
       <c r="K7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L7">
         <v>10</v>
@@ -1079,7 +1052,7 @@
         <v>10</v>
       </c>
       <c r="K8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L8">
         <v>8</v>
@@ -1115,7 +1088,7 @@
         <v>10</v>
       </c>
       <c r="W8">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X8">
         <v>9</v>
@@ -1156,7 +1129,7 @@
         <v>10</v>
       </c>
       <c r="K9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L9">
         <v>9</v>
@@ -1233,7 +1206,7 @@
         <v>8</v>
       </c>
       <c r="K10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L10">
         <v>8</v>
@@ -1269,7 +1242,7 @@
         <v>8</v>
       </c>
       <c r="W10">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X10">
         <v>9</v>
@@ -1310,7 +1283,7 @@
         <v>9</v>
       </c>
       <c r="K11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L11">
         <v>6</v>
@@ -1346,7 +1319,7 @@
         <v>8</v>
       </c>
       <c r="W11">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="X11">
         <v>7</v>
@@ -1387,7 +1360,7 @@
         <v>9</v>
       </c>
       <c r="K12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L12">
         <v>8</v>
@@ -1464,7 +1437,7 @@
         <v>8</v>
       </c>
       <c r="K13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L13">
         <v>10</v>
@@ -1500,7 +1473,7 @@
         <v>9</v>
       </c>
       <c r="W13">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="X13">
         <v>10</v>
@@ -1541,7 +1514,7 @@
         <v>10</v>
       </c>
       <c r="K14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L14">
         <v>9</v>
@@ -1618,7 +1591,7 @@
         <v>10</v>
       </c>
       <c r="K15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L15">
         <v>7</v>
@@ -1695,7 +1668,7 @@
         <v>10</v>
       </c>
       <c r="K16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L16">
         <v>9</v>
@@ -1731,7 +1704,7 @@
         <v>10</v>
       </c>
       <c r="W16">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X16">
         <v>9</v>
@@ -1772,7 +1745,7 @@
         <v>9</v>
       </c>
       <c r="K17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L17">
         <v>8</v>
@@ -1808,7 +1781,7 @@
         <v>10</v>
       </c>
       <c r="W17">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X17">
         <v>9</v>
@@ -1849,7 +1822,7 @@
         <v>10</v>
       </c>
       <c r="K18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L18">
         <v>7</v>
@@ -1926,7 +1899,7 @@
         <v>8</v>
       </c>
       <c r="K19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L19">
         <v>7</v>
@@ -2003,7 +1976,7 @@
         <v>8</v>
       </c>
       <c r="K20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L20">
         <v>8</v>
@@ -2080,7 +2053,7 @@
         <v>9</v>
       </c>
       <c r="K21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L21">
         <v>8</v>
@@ -2116,7 +2089,7 @@
         <v>10</v>
       </c>
       <c r="W21">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X21">
         <v>9</v>
@@ -2157,7 +2130,7 @@
         <v>10</v>
       </c>
       <c r="K22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L22">
         <v>10</v>
@@ -2234,7 +2207,7 @@
         <v>10</v>
       </c>
       <c r="K23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L23">
         <v>9</v>
@@ -2270,7 +2243,7 @@
         <v>10</v>
       </c>
       <c r="W23">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X23">
         <v>9</v>
@@ -2311,7 +2284,7 @@
         <v>10</v>
       </c>
       <c r="K24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L24">
         <v>10</v>
@@ -2388,7 +2361,7 @@
         <v>9</v>
       </c>
       <c r="K25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L25">
         <v>8</v>
@@ -2424,7 +2397,7 @@
         <v>9</v>
       </c>
       <c r="W25">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="X25">
         <v>9</v>
@@ -2465,7 +2438,7 @@
         <v>8</v>
       </c>
       <c r="K26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L26">
         <v>7</v>
@@ -2542,7 +2515,7 @@
         <v>8</v>
       </c>
       <c r="K27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L27">
         <v>8</v>
@@ -2619,7 +2592,7 @@
         <v>8</v>
       </c>
       <c r="K28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L28">
         <v>9</v>
@@ -2655,7 +2628,7 @@
         <v>9</v>
       </c>
       <c r="W28">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X28">
         <v>10</v>
@@ -2696,7 +2669,7 @@
         <v>7</v>
       </c>
       <c r="K29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L29">
         <v>7</v>
@@ -2732,7 +2705,7 @@
         <v>8</v>
       </c>
       <c r="W29">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="X29">
         <v>8</v>
@@ -2773,7 +2746,7 @@
         <v>9</v>
       </c>
       <c r="K30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L30">
         <v>10</v>
@@ -2850,7 +2823,7 @@
         <v>10</v>
       </c>
       <c r="K31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L31">
         <v>9</v>
@@ -2927,7 +2900,7 @@
         <v>10</v>
       </c>
       <c r="K32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L32">
         <v>9</v>
@@ -2963,7 +2936,7 @@
         <v>10</v>
       </c>
       <c r="W32">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X32">
         <v>9</v>
@@ -3004,7 +2977,7 @@
         <v>10</v>
       </c>
       <c r="K33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L33">
         <v>10</v>
@@ -3040,7 +3013,7 @@
         <v>10</v>
       </c>
       <c r="W33">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X33">
         <v>10</v>
@@ -3081,7 +3054,7 @@
         <v>9</v>
       </c>
       <c r="K34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L34">
         <v>8</v>
@@ -3117,7 +3090,7 @@
         <v>10</v>
       </c>
       <c r="W34">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X34">
         <v>9</v>
@@ -3158,7 +3131,7 @@
         <v>10</v>
       </c>
       <c r="K35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L35">
         <v>10</v>
@@ -3194,7 +3167,7 @@
         <v>10</v>
       </c>
       <c r="W35">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X35">
         <v>10</v>
@@ -3235,7 +3208,7 @@
         <v>10</v>
       </c>
       <c r="K36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L36">
         <v>10</v>
@@ -3271,7 +3244,7 @@
         <v>10</v>
       </c>
       <c r="W36">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="X36">
         <v>10</v>
@@ -3312,7 +3285,7 @@
         <v>10</v>
       </c>
       <c r="K37">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L37">
         <v>10</v>
@@ -3499,7 +3472,7 @@
         <v>100</v>
       </c>
       <c r="K4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L4">
         <v>100</v>
@@ -3558,7 +3531,7 @@
         <v>100</v>
       </c>
       <c r="K5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L5">
         <v>100</v>
@@ -3617,7 +3590,7 @@
         <v>100</v>
       </c>
       <c r="K6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L6">
         <v>100</v>
@@ -3676,7 +3649,7 @@
         <v>100</v>
       </c>
       <c r="K7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L7">
         <v>100</v>
@@ -3735,7 +3708,7 @@
         <v>100</v>
       </c>
       <c r="K8">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L8">
         <v>100</v>
@@ -3794,7 +3767,7 @@
         <v>100</v>
       </c>
       <c r="K9">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L9">
         <v>80</v>
@@ -3853,7 +3826,7 @@
         <v>100</v>
       </c>
       <c r="K10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L10">
         <v>100</v>
@@ -3912,7 +3885,7 @@
         <v>100</v>
       </c>
       <c r="K11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L11">
         <v>100</v>
@@ -3971,7 +3944,7 @@
         <v>100</v>
       </c>
       <c r="K12">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L12">
         <v>100</v>
@@ -4030,7 +4003,7 @@
         <v>100</v>
       </c>
       <c r="K13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L13">
         <v>100</v>
@@ -4089,7 +4062,7 @@
         <v>100</v>
       </c>
       <c r="K14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L14">
         <v>100</v>
@@ -4148,7 +4121,7 @@
         <v>100</v>
       </c>
       <c r="K15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L15">
         <v>100</v>
@@ -4207,7 +4180,7 @@
         <v>100</v>
       </c>
       <c r="K16">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L16">
         <v>100</v>
@@ -4266,7 +4239,7 @@
         <v>100</v>
       </c>
       <c r="K17">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L17">
         <v>100</v>
@@ -4325,7 +4298,7 @@
         <v>100</v>
       </c>
       <c r="K18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L18">
         <v>100</v>
@@ -4384,7 +4357,7 @@
         <v>100</v>
       </c>
       <c r="K19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L19">
         <v>100</v>
@@ -4443,7 +4416,7 @@
         <v>100</v>
       </c>
       <c r="K20">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L20">
         <v>100</v>
@@ -4502,7 +4475,7 @@
         <v>100</v>
       </c>
       <c r="K21">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L21">
         <v>100</v>
@@ -4561,7 +4534,7 @@
         <v>100</v>
       </c>
       <c r="K22">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L22">
         <v>100</v>
@@ -4620,7 +4593,7 @@
         <v>100</v>
       </c>
       <c r="K23">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L23">
         <v>100</v>
@@ -4679,7 +4652,7 @@
         <v>100</v>
       </c>
       <c r="K24">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L24">
         <v>100</v>
@@ -4738,7 +4711,7 @@
         <v>100</v>
       </c>
       <c r="K25">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L25">
         <v>100</v>
@@ -4797,7 +4770,7 @@
         <v>100</v>
       </c>
       <c r="K26">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L26">
         <v>100</v>
@@ -4856,7 +4829,7 @@
         <v>100</v>
       </c>
       <c r="K27">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L27">
         <v>100</v>
@@ -4915,7 +4888,7 @@
         <v>100</v>
       </c>
       <c r="K28">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L28">
         <v>100</v>
@@ -4974,7 +4947,7 @@
         <v>100</v>
       </c>
       <c r="K29">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L29">
         <v>100</v>
@@ -5033,7 +5006,7 @@
         <v>100</v>
       </c>
       <c r="K30">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L30">
         <v>100</v>
@@ -5092,7 +5065,7 @@
         <v>100</v>
       </c>
       <c r="K31">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L31">
         <v>100</v>
@@ -5151,7 +5124,7 @@
         <v>100</v>
       </c>
       <c r="K32">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L32">
         <v>100</v>
@@ -5210,7 +5183,7 @@
         <v>100</v>
       </c>
       <c r="K33">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L33">
         <v>100</v>
@@ -5269,7 +5242,7 @@
         <v>100</v>
       </c>
       <c r="K34">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L34">
         <v>100</v>
@@ -5328,7 +5301,7 @@
         <v>100</v>
       </c>
       <c r="K35">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L35">
         <v>100</v>
@@ -5387,7 +5360,7 @@
         <v>100</v>
       </c>
       <c r="K36">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L36">
         <v>100</v>
@@ -5446,7 +5419,7 @@
         <v>100</v>
       </c>
       <c r="K37">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L37">
         <v>100</v>
@@ -5527,7 +5500,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B2" t="s">
         <v>58</v>
@@ -5536,19 +5509,19 @@
         <v>34</v>
       </c>
       <c r="D2">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F2" s="2">
-        <v>91.2</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="G2" s="2">
-        <v>8.800000000000001</v>
+        <v>2.9</v>
       </c>
       <c r="H2">
-        <v>7.6</v>
+        <v>8.5</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -5559,7 +5532,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B3" t="s">
         <v>59</v>
@@ -5568,19 +5541,19 @@
         <v>34</v>
       </c>
       <c r="D3">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F3" s="2">
-        <v>97.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="G3" s="2">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="H3">
-        <v>8.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -5758,7 +5731,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5790,93 +5763,24 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>20330051920226</v>
+        <v>20330051920236</v>
       </c>
       <c r="B2" t="s">
         <v>67</v>
       </c>
       <c r="C2" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="D2" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="E2" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F2" t="s">
         <v>58</v>
       </c>
       <c r="G2">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3">
-        <v>20330051920236</v>
-      </c>
-      <c r="B3" t="s">
-        <v>68</v>
-      </c>
-      <c r="C3" t="s">
-        <v>72</v>
-      </c>
-      <c r="D3" t="s">
-        <v>76</v>
-      </c>
-      <c r="E3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F3" t="s">
-        <v>59</v>
-      </c>
-      <c r="G3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4">
-        <v>20330051920240</v>
-      </c>
-      <c r="B4" t="s">
-        <v>69</v>
-      </c>
-      <c r="C4" t="s">
-        <v>73</v>
-      </c>
-      <c r="D4" t="s">
-        <v>77</v>
-      </c>
-      <c r="E4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F4" t="s">
-        <v>58</v>
-      </c>
-      <c r="G4">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5">
-        <v>20330051920251</v>
-      </c>
-      <c r="B5" t="s">
-        <v>70</v>
-      </c>
-      <c r="C5" t="s">
-        <v>74</v>
-      </c>
-      <c r="D5" t="s">
-        <v>78</v>
-      </c>
-      <c r="E5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F5" t="s">
-        <v>58</v>
-      </c>
-      <c r="G5">
         <v>5</v>
       </c>
     </row>

--- a/grupos/6ALCM - Estadisticos 20222.xlsx
+++ b/grupos/6ALCM - Estadisticos 20222.xlsx
@@ -3454,19 +3454,19 @@
         <v>100</v>
       </c>
       <c r="E4">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="F4">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="G4">
         <v>92</v>
       </c>
       <c r="H4">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="I4">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="J4">
         <v>100</v>
@@ -3478,25 +3478,25 @@
         <v>100</v>
       </c>
       <c r="M4">
-        <v>92</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="N4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S4">
-        <v>0</v>
+        <v>93.90000000000001</v>
       </c>
     </row>
     <row r="5" spans="1:19">
@@ -3513,49 +3513,49 @@
         <v>100</v>
       </c>
       <c r="E5">
-        <v>88</v>
+        <v>91.7</v>
       </c>
       <c r="F5">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="G5">
         <v>80</v>
       </c>
       <c r="H5">
-        <v>112.5</v>
+        <v>94.3</v>
       </c>
       <c r="I5">
-        <v>110</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="J5">
         <v>100</v>
       </c>
       <c r="K5">
-        <v>100</v>
+        <v>95.90000000000001</v>
       </c>
       <c r="L5">
         <v>100</v>
       </c>
       <c r="M5">
-        <v>88</v>
+        <v>85.7</v>
       </c>
       <c r="N5">
-        <v>0</v>
+        <v>94.3</v>
       </c>
       <c r="O5">
-        <v>0</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="P5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q5">
-        <v>0</v>
+        <v>95.90000000000001</v>
       </c>
       <c r="R5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S5">
-        <v>0</v>
+        <v>85.7</v>
       </c>
     </row>
     <row r="6" spans="1:19">
@@ -3572,49 +3572,49 @@
         <v>100</v>
       </c>
       <c r="E6">
-        <v>88</v>
+        <v>91.7</v>
       </c>
       <c r="F6">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="G6">
         <v>92</v>
       </c>
       <c r="H6">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="I6">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="J6">
         <v>100</v>
       </c>
       <c r="K6">
-        <v>100</v>
+        <v>95.90000000000001</v>
       </c>
       <c r="L6">
         <v>100</v>
       </c>
       <c r="M6">
-        <v>92</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="N6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q6">
-        <v>0</v>
+        <v>95.90000000000001</v>
       </c>
       <c r="R6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S6">
-        <v>0</v>
+        <v>93.90000000000001</v>
       </c>
     </row>
     <row r="7" spans="1:19">
@@ -3631,49 +3631,49 @@
         <v>100</v>
       </c>
       <c r="E7">
-        <v>92</v>
+        <v>95.8</v>
       </c>
       <c r="F7">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="G7">
         <v>100</v>
       </c>
       <c r="H7">
-        <v>112.5</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="I7">
-        <v>110</v>
+        <v>95.5</v>
       </c>
       <c r="J7">
         <v>100</v>
       </c>
       <c r="K7">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="L7">
         <v>100</v>
       </c>
       <c r="M7">
-        <v>80</v>
+        <v>91.8</v>
       </c>
       <c r="N7">
-        <v>0</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="O7">
-        <v>0</v>
+        <v>95.5</v>
       </c>
       <c r="P7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q7">
-        <v>0</v>
+        <v>98</v>
       </c>
       <c r="R7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S7">
-        <v>0</v>
+        <v>91.8</v>
       </c>
     </row>
     <row r="8" spans="1:19">
@@ -3690,19 +3690,19 @@
         <v>100</v>
       </c>
       <c r="E8">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="F8">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="G8">
         <v>100</v>
       </c>
       <c r="H8">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="I8">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="J8">
         <v>100</v>
@@ -3714,25 +3714,25 @@
         <v>100</v>
       </c>
       <c r="M8">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="N8">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O8">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P8">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q8">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R8">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S8">
-        <v>0</v>
+        <v>98</v>
       </c>
     </row>
     <row r="9" spans="1:19">
@@ -3749,19 +3749,19 @@
         <v>100</v>
       </c>
       <c r="E9">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="F9">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="G9">
         <v>100</v>
       </c>
       <c r="H9">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="I9">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="J9">
         <v>100</v>
@@ -3770,28 +3770,28 @@
         <v>100</v>
       </c>
       <c r="L9">
-        <v>80</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="M9">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="N9">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O9">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P9">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q9">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R9">
-        <v>0</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="S9">
-        <v>0</v>
+        <v>98</v>
       </c>
     </row>
     <row r="10" spans="1:19">
@@ -3808,49 +3808,49 @@
         <v>100</v>
       </c>
       <c r="E10">
-        <v>80</v>
+        <v>83.3</v>
       </c>
       <c r="F10">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="G10">
         <v>92</v>
       </c>
       <c r="H10">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="I10">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="J10">
         <v>100</v>
       </c>
       <c r="K10">
-        <v>100</v>
+        <v>91.8</v>
       </c>
       <c r="L10">
         <v>100</v>
       </c>
       <c r="M10">
-        <v>84</v>
+        <v>89.8</v>
       </c>
       <c r="N10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q10">
-        <v>0</v>
+        <v>91.8</v>
       </c>
       <c r="R10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S10">
-        <v>0</v>
+        <v>89.8</v>
       </c>
     </row>
     <row r="11" spans="1:19">
@@ -3867,49 +3867,49 @@
         <v>100</v>
       </c>
       <c r="E11">
-        <v>84</v>
+        <v>87.5</v>
       </c>
       <c r="F11">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="G11">
         <v>88</v>
       </c>
       <c r="H11">
-        <v>112.5</v>
+        <v>93.2</v>
       </c>
       <c r="I11">
-        <v>110</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="J11">
         <v>100</v>
       </c>
       <c r="K11">
-        <v>100</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="L11">
         <v>100</v>
       </c>
       <c r="M11">
-        <v>80</v>
+        <v>85.7</v>
       </c>
       <c r="N11">
-        <v>0</v>
+        <v>93.2</v>
       </c>
       <c r="O11">
-        <v>0</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="P11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q11">
-        <v>0</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="R11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S11">
-        <v>0</v>
+        <v>85.7</v>
       </c>
     </row>
     <row r="12" spans="1:19">
@@ -3926,19 +3926,19 @@
         <v>100</v>
       </c>
       <c r="E12">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="F12">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="G12">
         <v>100</v>
       </c>
       <c r="H12">
-        <v>115</v>
+        <v>97.7</v>
       </c>
       <c r="I12">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="J12">
         <v>100</v>
@@ -3950,25 +3950,25 @@
         <v>100</v>
       </c>
       <c r="M12">
-        <v>88</v>
+        <v>95.90000000000001</v>
       </c>
       <c r="N12">
-        <v>0</v>
+        <v>97.7</v>
       </c>
       <c r="O12">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P12">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q12">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R12">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S12">
-        <v>0</v>
+        <v>95.90000000000001</v>
       </c>
     </row>
     <row r="13" spans="1:19">
@@ -3985,49 +3985,49 @@
         <v>100</v>
       </c>
       <c r="E13">
-        <v>92</v>
+        <v>95.8</v>
       </c>
       <c r="F13">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="G13">
         <v>92</v>
       </c>
       <c r="H13">
-        <v>115</v>
+        <v>97.7</v>
       </c>
       <c r="I13">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="J13">
         <v>100</v>
       </c>
       <c r="K13">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="L13">
         <v>100</v>
       </c>
       <c r="M13">
-        <v>92</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="N13">
-        <v>0</v>
+        <v>97.7</v>
       </c>
       <c r="O13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q13">
-        <v>0</v>
+        <v>98</v>
       </c>
       <c r="R13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S13">
-        <v>0</v>
+        <v>93.90000000000001</v>
       </c>
     </row>
     <row r="14" spans="1:19">
@@ -4044,19 +4044,19 @@
         <v>100</v>
       </c>
       <c r="E14">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="F14">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="G14">
         <v>100</v>
       </c>
       <c r="H14">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="I14">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="J14">
         <v>100</v>
@@ -4068,25 +4068,25 @@
         <v>100</v>
       </c>
       <c r="M14">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="N14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S14">
-        <v>0</v>
+        <v>98</v>
       </c>
     </row>
     <row r="15" spans="1:19">
@@ -4103,19 +4103,19 @@
         <v>100</v>
       </c>
       <c r="E15">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="F15">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="G15">
         <v>100</v>
       </c>
       <c r="H15">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="I15">
-        <v>115</v>
+        <v>97.7</v>
       </c>
       <c r="J15">
         <v>100</v>
@@ -4127,25 +4127,25 @@
         <v>100</v>
       </c>
       <c r="M15">
-        <v>80</v>
+        <v>91.8</v>
       </c>
       <c r="N15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O15">
-        <v>0</v>
+        <v>97.7</v>
       </c>
       <c r="P15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S15">
-        <v>0</v>
+        <v>91.8</v>
       </c>
     </row>
     <row r="16" spans="1:19">
@@ -4162,19 +4162,19 @@
         <v>100</v>
       </c>
       <c r="E16">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="F16">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="G16">
         <v>100</v>
       </c>
       <c r="H16">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="I16">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="J16">
         <v>100</v>
@@ -4186,25 +4186,25 @@
         <v>100</v>
       </c>
       <c r="M16">
-        <v>88</v>
+        <v>95.90000000000001</v>
       </c>
       <c r="N16">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O16">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P16">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q16">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R16">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S16">
-        <v>0</v>
+        <v>95.90000000000001</v>
       </c>
     </row>
     <row r="17" spans="1:19">
@@ -4221,49 +4221,49 @@
         <v>100</v>
       </c>
       <c r="E17">
-        <v>88</v>
+        <v>91.7</v>
       </c>
       <c r="F17">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="G17">
         <v>80</v>
       </c>
       <c r="H17">
-        <v>112.5</v>
+        <v>94.3</v>
       </c>
       <c r="I17">
-        <v>110</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="J17">
         <v>100</v>
       </c>
       <c r="K17">
-        <v>100</v>
+        <v>95.90000000000001</v>
       </c>
       <c r="L17">
         <v>100</v>
       </c>
       <c r="M17">
-        <v>88</v>
+        <v>85.7</v>
       </c>
       <c r="N17">
-        <v>0</v>
+        <v>94.3</v>
       </c>
       <c r="O17">
-        <v>0</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="P17">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q17">
-        <v>0</v>
+        <v>95.90000000000001</v>
       </c>
       <c r="R17">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S17">
-        <v>0</v>
+        <v>85.7</v>
       </c>
     </row>
     <row r="18" spans="1:19">
@@ -4280,49 +4280,49 @@
         <v>100</v>
       </c>
       <c r="E18">
-        <v>92</v>
+        <v>95.8</v>
       </c>
       <c r="F18">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="G18">
         <v>100</v>
       </c>
       <c r="H18">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="I18">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="J18">
         <v>100</v>
       </c>
       <c r="K18">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="L18">
         <v>100</v>
       </c>
       <c r="M18">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="N18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q18">
-        <v>0</v>
+        <v>98</v>
       </c>
       <c r="R18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S18">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="19" spans="1:19">
@@ -4339,49 +4339,49 @@
         <v>100</v>
       </c>
       <c r="E19">
-        <v>88</v>
+        <v>91.7</v>
       </c>
       <c r="F19">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="G19">
         <v>92</v>
       </c>
       <c r="H19">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="I19">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="J19">
         <v>100</v>
       </c>
       <c r="K19">
-        <v>100</v>
+        <v>95.90000000000001</v>
       </c>
       <c r="L19">
         <v>100</v>
       </c>
       <c r="M19">
-        <v>88</v>
+        <v>91.8</v>
       </c>
       <c r="N19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q19">
-        <v>0</v>
+        <v>95.90000000000001</v>
       </c>
       <c r="R19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S19">
-        <v>0</v>
+        <v>91.8</v>
       </c>
     </row>
     <row r="20" spans="1:19">
@@ -4398,49 +4398,49 @@
         <v>100</v>
       </c>
       <c r="E20">
-        <v>92</v>
+        <v>95.8</v>
       </c>
       <c r="F20">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="G20">
         <v>88</v>
       </c>
       <c r="H20">
-        <v>112.5</v>
+        <v>93.2</v>
       </c>
       <c r="I20">
-        <v>110</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="J20">
         <v>100</v>
       </c>
       <c r="K20">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="L20">
         <v>100</v>
       </c>
       <c r="M20">
-        <v>80</v>
+        <v>85.7</v>
       </c>
       <c r="N20">
-        <v>0</v>
+        <v>93.2</v>
       </c>
       <c r="O20">
-        <v>0</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="P20">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q20">
-        <v>0</v>
+        <v>98</v>
       </c>
       <c r="R20">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S20">
-        <v>0</v>
+        <v>85.7</v>
       </c>
     </row>
     <row r="21" spans="1:19">
@@ -4457,19 +4457,19 @@
         <v>100</v>
       </c>
       <c r="E21">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="F21">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="G21">
         <v>100</v>
       </c>
       <c r="H21">
-        <v>115</v>
+        <v>97.7</v>
       </c>
       <c r="I21">
-        <v>110</v>
+        <v>95.5</v>
       </c>
       <c r="J21">
         <v>100</v>
@@ -4481,25 +4481,25 @@
         <v>100</v>
       </c>
       <c r="M21">
-        <v>72</v>
+        <v>87.8</v>
       </c>
       <c r="N21">
-        <v>0</v>
+        <v>97.7</v>
       </c>
       <c r="O21">
-        <v>0</v>
+        <v>95.5</v>
       </c>
       <c r="P21">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q21">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R21">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S21">
-        <v>0</v>
+        <v>87.8</v>
       </c>
     </row>
     <row r="22" spans="1:19">
@@ -4516,19 +4516,19 @@
         <v>100</v>
       </c>
       <c r="E22">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="F22">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="G22">
         <v>100</v>
       </c>
       <c r="H22">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="I22">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="J22">
         <v>100</v>
@@ -4540,25 +4540,25 @@
         <v>100</v>
       </c>
       <c r="M22">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="N22">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O22">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P22">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q22">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R22">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S22">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="23" spans="1:19">
@@ -4575,49 +4575,49 @@
         <v>100</v>
       </c>
       <c r="E23">
-        <v>92</v>
+        <v>95.8</v>
       </c>
       <c r="F23">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="G23">
         <v>88</v>
       </c>
       <c r="H23">
-        <v>115</v>
+        <v>97.7</v>
       </c>
       <c r="I23">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="J23">
         <v>100</v>
       </c>
       <c r="K23">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="L23">
         <v>100</v>
       </c>
       <c r="M23">
-        <v>92</v>
+        <v>91.8</v>
       </c>
       <c r="N23">
-        <v>0</v>
+        <v>97.7</v>
       </c>
       <c r="O23">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P23">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q23">
-        <v>0</v>
+        <v>98</v>
       </c>
       <c r="R23">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S23">
-        <v>0</v>
+        <v>91.8</v>
       </c>
     </row>
     <row r="24" spans="1:19">
@@ -4634,19 +4634,19 @@
         <v>100</v>
       </c>
       <c r="E24">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="F24">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="G24">
         <v>100</v>
       </c>
       <c r="H24">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="I24">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="J24">
         <v>100</v>
@@ -4658,25 +4658,25 @@
         <v>100</v>
       </c>
       <c r="M24">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="N24">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O24">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P24">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q24">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R24">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S24">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="25" spans="1:19">
@@ -4693,49 +4693,49 @@
         <v>100</v>
       </c>
       <c r="E25">
-        <v>88</v>
+        <v>91.7</v>
       </c>
       <c r="F25">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="G25">
         <v>100</v>
       </c>
       <c r="H25">
-        <v>117.5</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="I25">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="J25">
         <v>100</v>
       </c>
       <c r="K25">
-        <v>100</v>
+        <v>95.90000000000001</v>
       </c>
       <c r="L25">
         <v>100</v>
       </c>
       <c r="M25">
-        <v>80</v>
+        <v>91.8</v>
       </c>
       <c r="N25">
-        <v>0</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="O25">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P25">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q25">
-        <v>0</v>
+        <v>95.90000000000001</v>
       </c>
       <c r="R25">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S25">
-        <v>0</v>
+        <v>91.8</v>
       </c>
     </row>
     <row r="26" spans="1:19">
@@ -4752,49 +4752,49 @@
         <v>100</v>
       </c>
       <c r="E26">
+        <v>83.3</v>
+      </c>
+      <c r="F26">
         <v>80</v>
-      </c>
-      <c r="F26">
-        <v>64</v>
       </c>
       <c r="G26">
         <v>80</v>
       </c>
       <c r="H26">
-        <v>112.5</v>
+        <v>94.3</v>
       </c>
       <c r="I26">
-        <v>110</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="J26">
         <v>100</v>
       </c>
       <c r="K26">
-        <v>100</v>
+        <v>91.8</v>
       </c>
       <c r="L26">
-        <v>100</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="M26">
-        <v>68</v>
+        <v>75.5</v>
       </c>
       <c r="N26">
-        <v>0</v>
+        <v>94.3</v>
       </c>
       <c r="O26">
-        <v>0</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="P26">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q26">
-        <v>0</v>
+        <v>91.8</v>
       </c>
       <c r="R26">
-        <v>0</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="S26">
-        <v>0</v>
+        <v>75.5</v>
       </c>
     </row>
     <row r="27" spans="1:19">
@@ -4811,49 +4811,49 @@
         <v>100</v>
       </c>
       <c r="E27">
-        <v>88</v>
+        <v>91.7</v>
       </c>
       <c r="F27">
-        <v>68</v>
+        <v>85</v>
       </c>
       <c r="G27">
         <v>80</v>
       </c>
       <c r="H27">
-        <v>112.5</v>
+        <v>94.3</v>
       </c>
       <c r="I27">
-        <v>110</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="J27">
         <v>100</v>
       </c>
       <c r="K27">
-        <v>100</v>
+        <v>95.90000000000001</v>
       </c>
       <c r="L27">
-        <v>100</v>
+        <v>93.3</v>
       </c>
       <c r="M27">
-        <v>72</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="N27">
-        <v>0</v>
+        <v>94.3</v>
       </c>
       <c r="O27">
-        <v>0</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="P27">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q27">
-        <v>0</v>
+        <v>95.90000000000001</v>
       </c>
       <c r="R27">
-        <v>0</v>
+        <v>93.3</v>
       </c>
       <c r="S27">
-        <v>0</v>
+        <v>77.59999999999999</v>
       </c>
     </row>
     <row r="28" spans="1:19">
@@ -4870,19 +4870,19 @@
         <v>100</v>
       </c>
       <c r="E28">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="F28">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="G28">
         <v>84</v>
       </c>
       <c r="H28">
-        <v>115</v>
+        <v>97.7</v>
       </c>
       <c r="I28">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="J28">
         <v>100</v>
@@ -4894,25 +4894,25 @@
         <v>100</v>
       </c>
       <c r="M28">
-        <v>88</v>
+        <v>87.8</v>
       </c>
       <c r="N28">
-        <v>0</v>
+        <v>97.7</v>
       </c>
       <c r="O28">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P28">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q28">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R28">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S28">
-        <v>0</v>
+        <v>87.8</v>
       </c>
     </row>
     <row r="29" spans="1:19">
@@ -4929,49 +4929,49 @@
         <v>100</v>
       </c>
       <c r="E29">
-        <v>80</v>
+        <v>83.3</v>
       </c>
       <c r="F29">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="G29">
         <v>84</v>
       </c>
       <c r="H29">
-        <v>112.5</v>
+        <v>94.3</v>
       </c>
       <c r="I29">
-        <v>110</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="J29">
         <v>100</v>
       </c>
       <c r="K29">
-        <v>100</v>
+        <v>91.8</v>
       </c>
       <c r="L29">
         <v>100</v>
       </c>
       <c r="M29">
-        <v>80</v>
+        <v>83.7</v>
       </c>
       <c r="N29">
-        <v>0</v>
+        <v>94.3</v>
       </c>
       <c r="O29">
-        <v>0</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="P29">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q29">
-        <v>0</v>
+        <v>91.8</v>
       </c>
       <c r="R29">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S29">
-        <v>0</v>
+        <v>83.7</v>
       </c>
     </row>
     <row r="30" spans="1:19">
@@ -4988,19 +4988,19 @@
         <v>100</v>
       </c>
       <c r="E30">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="F30">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="G30">
         <v>100</v>
       </c>
       <c r="H30">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="I30">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="J30">
         <v>100</v>
@@ -5009,28 +5009,28 @@
         <v>100</v>
       </c>
       <c r="L30">
-        <v>100</v>
+        <v>77.8</v>
       </c>
       <c r="M30">
-        <v>88</v>
+        <v>95.90000000000001</v>
       </c>
       <c r="N30">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O30">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P30">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q30">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R30">
-        <v>0</v>
+        <v>77.8</v>
       </c>
       <c r="S30">
-        <v>0</v>
+        <v>95.90000000000001</v>
       </c>
     </row>
     <row r="31" spans="1:19">
@@ -5047,19 +5047,19 @@
         <v>100</v>
       </c>
       <c r="E31">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="F31">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="G31">
         <v>100</v>
       </c>
       <c r="H31">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="I31">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="J31">
         <v>100</v>
@@ -5071,25 +5071,25 @@
         <v>100</v>
       </c>
       <c r="M31">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="N31">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O31">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P31">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q31">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R31">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S31">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="32" spans="1:19">
@@ -5106,19 +5106,19 @@
         <v>100</v>
       </c>
       <c r="E32">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="F32">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="G32">
         <v>100</v>
       </c>
       <c r="H32">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="I32">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="J32">
         <v>100</v>
@@ -5130,25 +5130,25 @@
         <v>100</v>
       </c>
       <c r="M32">
-        <v>84</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="N32">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O32">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P32">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q32">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R32">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S32">
-        <v>0</v>
+        <v>93.90000000000001</v>
       </c>
     </row>
     <row r="33" spans="1:19">
@@ -5165,49 +5165,49 @@
         <v>100</v>
       </c>
       <c r="E33">
-        <v>88</v>
+        <v>91.7</v>
       </c>
       <c r="F33">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="G33">
         <v>100</v>
       </c>
       <c r="H33">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="I33">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="J33">
         <v>100</v>
       </c>
       <c r="K33">
-        <v>100</v>
+        <v>95.90000000000001</v>
       </c>
       <c r="L33">
         <v>100</v>
       </c>
       <c r="M33">
-        <v>88</v>
+        <v>95.90000000000001</v>
       </c>
       <c r="N33">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O33">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P33">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q33">
-        <v>0</v>
+        <v>95.90000000000001</v>
       </c>
       <c r="R33">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S33">
-        <v>0</v>
+        <v>95.90000000000001</v>
       </c>
     </row>
     <row r="34" spans="1:19">
@@ -5224,49 +5224,49 @@
         <v>100</v>
       </c>
       <c r="E34">
-        <v>88</v>
+        <v>91.7</v>
       </c>
       <c r="F34">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="G34">
         <v>100</v>
       </c>
       <c r="H34">
-        <v>112.5</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="I34">
-        <v>110</v>
+        <v>95.5</v>
       </c>
       <c r="J34">
         <v>100</v>
       </c>
       <c r="K34">
-        <v>100</v>
+        <v>95.90000000000001</v>
       </c>
       <c r="L34">
         <v>100</v>
       </c>
       <c r="M34">
-        <v>84</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="N34">
-        <v>0</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="O34">
-        <v>0</v>
+        <v>95.5</v>
       </c>
       <c r="P34">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q34">
-        <v>0</v>
+        <v>95.90000000000001</v>
       </c>
       <c r="R34">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S34">
-        <v>0</v>
+        <v>93.90000000000001</v>
       </c>
     </row>
     <row r="35" spans="1:19">
@@ -5283,19 +5283,19 @@
         <v>100</v>
       </c>
       <c r="E35">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="F35">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="G35">
         <v>100</v>
       </c>
       <c r="H35">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="I35">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="J35">
         <v>100</v>
@@ -5307,25 +5307,25 @@
         <v>100</v>
       </c>
       <c r="M35">
-        <v>80</v>
+        <v>91.8</v>
       </c>
       <c r="N35">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O35">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P35">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q35">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R35">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S35">
-        <v>0</v>
+        <v>91.8</v>
       </c>
     </row>
     <row r="36" spans="1:19">
@@ -5342,19 +5342,19 @@
         <v>100</v>
       </c>
       <c r="E36">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="F36">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="G36">
         <v>100</v>
       </c>
       <c r="H36">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="I36">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="J36">
         <v>100</v>
@@ -5366,25 +5366,25 @@
         <v>100</v>
       </c>
       <c r="M36">
-        <v>80</v>
+        <v>91.8</v>
       </c>
       <c r="N36">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O36">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P36">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q36">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R36">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S36">
-        <v>0</v>
+        <v>91.8</v>
       </c>
     </row>
     <row r="37" spans="1:19">
@@ -5401,19 +5401,19 @@
         <v>100</v>
       </c>
       <c r="E37">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="F37">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="G37">
         <v>100</v>
       </c>
       <c r="H37">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="I37">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="J37">
         <v>100</v>
@@ -5425,25 +5425,25 @@
         <v>100</v>
       </c>
       <c r="M37">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="N37">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O37">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P37">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q37">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R37">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S37">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
   </sheetData>

--- a/grupos/6ALCM - Estadisticos 20222.xlsx
+++ b/grupos/6ALCM - Estadisticos 20222.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="67">
   <si>
     <t>Materia</t>
   </si>
@@ -219,15 +219,6 @@
   </si>
   <si>
     <t>Nombres</t>
-  </si>
-  <si>
-    <t>MAZAHUA</t>
-  </si>
-  <si>
-    <t>ACEVEDO</t>
-  </si>
-  <si>
-    <t>GENARO RAFAEL</t>
   </si>
 </sst>
 </file>
@@ -753,22 +744,22 @@
         <v>9</v>
       </c>
       <c r="N4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T4">
         <v>10</v>
@@ -777,7 +768,7 @@
         <v>10</v>
       </c>
       <c r="V4">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W4">
         <v>10</v>
@@ -830,22 +821,22 @@
         <v>8</v>
       </c>
       <c r="N5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T5">
         <v>9</v>
@@ -907,22 +898,22 @@
         <v>7</v>
       </c>
       <c r="N6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T6">
         <v>10</v>
@@ -940,7 +931,7 @@
         <v>8</v>
       </c>
       <c r="Y6">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7" spans="1:25">
@@ -984,22 +975,22 @@
         <v>9</v>
       </c>
       <c r="N7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T7">
         <v>10</v>
@@ -1061,22 +1052,22 @@
         <v>9</v>
       </c>
       <c r="N8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T8">
         <v>9</v>
@@ -1138,22 +1129,22 @@
         <v>9</v>
       </c>
       <c r="N9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T9">
         <v>10</v>
@@ -1215,22 +1206,22 @@
         <v>7</v>
       </c>
       <c r="N10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T10">
         <v>10</v>
@@ -1292,22 +1283,22 @@
         <v>7</v>
       </c>
       <c r="N11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T11">
         <v>7</v>
@@ -1322,10 +1313,10 @@
         <v>7</v>
       </c>
       <c r="X11">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y11">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="12" spans="1:25">
@@ -1369,22 +1360,22 @@
         <v>9</v>
       </c>
       <c r="N12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T12">
         <v>9</v>
@@ -1393,7 +1384,7 @@
         <v>9</v>
       </c>
       <c r="V12">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W12">
         <v>7</v>
@@ -1446,22 +1437,22 @@
         <v>9</v>
       </c>
       <c r="N13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T13">
         <v>9</v>
@@ -1523,22 +1514,22 @@
         <v>10</v>
       </c>
       <c r="N14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T14">
         <v>10</v>
@@ -1600,22 +1591,22 @@
         <v>8</v>
       </c>
       <c r="N15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T15">
         <v>9</v>
@@ -1624,16 +1615,16 @@
         <v>9</v>
       </c>
       <c r="V15">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W15">
         <v>7</v>
       </c>
       <c r="X15">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y15">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="16" spans="1:25">
@@ -1677,22 +1668,22 @@
         <v>9</v>
       </c>
       <c r="N16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T16">
         <v>10</v>
@@ -1701,7 +1692,7 @@
         <v>10</v>
       </c>
       <c r="V16">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W16">
         <v>9</v>
@@ -1754,22 +1745,22 @@
         <v>9</v>
       </c>
       <c r="N17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T17">
         <v>9</v>
@@ -1778,7 +1769,7 @@
         <v>9</v>
       </c>
       <c r="V17">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W17">
         <v>7</v>
@@ -1831,22 +1822,22 @@
         <v>7</v>
       </c>
       <c r="N18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T18">
         <v>9</v>
@@ -1864,7 +1855,7 @@
         <v>8</v>
       </c>
       <c r="Y18">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="19" spans="1:25">
@@ -1908,22 +1899,22 @@
         <v>9</v>
       </c>
       <c r="N19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T19">
         <v>10</v>
@@ -1985,22 +1976,22 @@
         <v>6</v>
       </c>
       <c r="N20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T20">
         <v>8</v>
@@ -2015,7 +2006,7 @@
         <v>7</v>
       </c>
       <c r="X20">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y20">
         <v>7</v>
@@ -2062,22 +2053,22 @@
         <v>8</v>
       </c>
       <c r="N21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T21">
         <v>9</v>
@@ -2086,7 +2077,7 @@
         <v>9</v>
       </c>
       <c r="V21">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W21">
         <v>8</v>
@@ -2139,22 +2130,22 @@
         <v>10</v>
       </c>
       <c r="N22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T22">
         <v>10</v>
@@ -2172,7 +2163,7 @@
         <v>10</v>
       </c>
       <c r="Y22">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="23" spans="1:25">
@@ -2216,22 +2207,22 @@
         <v>8</v>
       </c>
       <c r="N23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T23">
         <v>9</v>
@@ -2293,22 +2284,22 @@
         <v>9</v>
       </c>
       <c r="N24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T24">
         <v>10</v>
@@ -2370,22 +2361,22 @@
         <v>9</v>
       </c>
       <c r="N25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T25">
         <v>10</v>
@@ -2394,7 +2385,7 @@
         <v>10</v>
       </c>
       <c r="V25">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W25">
         <v>7</v>
@@ -2447,28 +2438,28 @@
         <v>5</v>
       </c>
       <c r="N26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T26">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U26">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V26">
         <v>7</v>
@@ -2477,10 +2468,10 @@
         <v>7</v>
       </c>
       <c r="X26">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y26">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="27" spans="1:25">
@@ -2524,22 +2515,22 @@
         <v>6</v>
       </c>
       <c r="N27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T27">
         <v>8</v>
@@ -2554,7 +2545,7 @@
         <v>7</v>
       </c>
       <c r="X27">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y27">
         <v>7</v>
@@ -2601,22 +2592,22 @@
         <v>8</v>
       </c>
       <c r="N28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T28">
         <v>8</v>
@@ -2631,7 +2622,7 @@
         <v>8</v>
       </c>
       <c r="X28">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y28">
         <v>8</v>
@@ -2678,22 +2669,22 @@
         <v>8</v>
       </c>
       <c r="N29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T29">
         <v>8</v>
@@ -2708,7 +2699,7 @@
         <v>8</v>
       </c>
       <c r="X29">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y29">
         <v>7</v>
@@ -2755,22 +2746,22 @@
         <v>10</v>
       </c>
       <c r="N30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T30">
         <v>10</v>
@@ -2779,7 +2770,7 @@
         <v>10</v>
       </c>
       <c r="V30">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W30">
         <v>10</v>
@@ -2826,28 +2817,28 @@
         <v>8</v>
       </c>
       <c r="L31">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="M31">
         <v>10</v>
       </c>
       <c r="N31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T31">
         <v>10</v>
@@ -2909,22 +2900,22 @@
         <v>9</v>
       </c>
       <c r="N32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T32">
         <v>9</v>
@@ -2942,7 +2933,7 @@
         <v>9</v>
       </c>
       <c r="Y32">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="33" spans="1:25">
@@ -2986,22 +2977,22 @@
         <v>9</v>
       </c>
       <c r="N33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T33">
         <v>10</v>
@@ -3063,22 +3054,22 @@
         <v>8</v>
       </c>
       <c r="N34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T34">
         <v>9</v>
@@ -3087,7 +3078,7 @@
         <v>9</v>
       </c>
       <c r="V34">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W34">
         <v>8</v>
@@ -3140,22 +3131,22 @@
         <v>10</v>
       </c>
       <c r="N35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T35">
         <v>10</v>
@@ -3170,7 +3161,7 @@
         <v>9</v>
       </c>
       <c r="X35">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y35">
         <v>10</v>
@@ -3217,22 +3208,22 @@
         <v>10</v>
       </c>
       <c r="N36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q36">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R36">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T36">
         <v>10</v>
@@ -3247,7 +3238,7 @@
         <v>9</v>
       </c>
       <c r="X36">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y36">
         <v>10</v>
@@ -3294,22 +3285,22 @@
         <v>10</v>
       </c>
       <c r="N37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q37">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T37">
         <v>10</v>
@@ -3490,13 +3481,13 @@
         <v>100</v>
       </c>
       <c r="Q4">
-        <v>100</v>
+        <v>98.8</v>
       </c>
       <c r="R4">
         <v>100</v>
       </c>
       <c r="S4">
-        <v>93.90000000000001</v>
+        <v>96.2</v>
       </c>
     </row>
     <row r="5" spans="1:19">
@@ -3540,22 +3531,22 @@
         <v>85.7</v>
       </c>
       <c r="N5">
-        <v>94.3</v>
+        <v>94.5</v>
       </c>
       <c r="O5">
-        <v>90.90000000000001</v>
+        <v>93.8</v>
       </c>
       <c r="P5">
         <v>100</v>
       </c>
       <c r="Q5">
-        <v>95.90000000000001</v>
+        <v>96.3</v>
       </c>
       <c r="R5">
         <v>100</v>
       </c>
       <c r="S5">
-        <v>85.7</v>
+        <v>91.09999999999999</v>
       </c>
     </row>
     <row r="6" spans="1:19">
@@ -3608,13 +3599,13 @@
         <v>100</v>
       </c>
       <c r="Q6">
-        <v>95.90000000000001</v>
+        <v>95</v>
       </c>
       <c r="R6">
         <v>100</v>
       </c>
       <c r="S6">
-        <v>93.90000000000001</v>
+        <v>96.2</v>
       </c>
     </row>
     <row r="7" spans="1:19">
@@ -3658,22 +3649,22 @@
         <v>91.8</v>
       </c>
       <c r="N7">
-        <v>96.59999999999999</v>
+        <v>96.09999999999999</v>
       </c>
       <c r="O7">
-        <v>95.5</v>
+        <v>93.8</v>
       </c>
       <c r="P7">
         <v>100</v>
       </c>
       <c r="Q7">
-        <v>98</v>
+        <v>96.3</v>
       </c>
       <c r="R7">
         <v>100</v>
       </c>
       <c r="S7">
-        <v>91.8</v>
+        <v>94.90000000000001</v>
       </c>
     </row>
     <row r="8" spans="1:19">
@@ -3726,13 +3717,13 @@
         <v>100</v>
       </c>
       <c r="Q8">
-        <v>100</v>
+        <v>98.8</v>
       </c>
       <c r="R8">
         <v>100</v>
       </c>
       <c r="S8">
-        <v>98</v>
+        <v>98.7</v>
       </c>
     </row>
     <row r="9" spans="1:19">
@@ -3770,7 +3761,7 @@
         <v>100</v>
       </c>
       <c r="L9">
-        <v>88.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="M9">
         <v>98</v>
@@ -3785,13 +3776,13 @@
         <v>100</v>
       </c>
       <c r="Q9">
-        <v>100</v>
+        <v>98.8</v>
       </c>
       <c r="R9">
-        <v>88.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="S9">
-        <v>98</v>
+        <v>98.7</v>
       </c>
     </row>
     <row r="10" spans="1:19">
@@ -3844,13 +3835,13 @@
         <v>100</v>
       </c>
       <c r="Q10">
-        <v>91.8</v>
+        <v>93.8</v>
       </c>
       <c r="R10">
         <v>100</v>
       </c>
       <c r="S10">
-        <v>89.8</v>
+        <v>93.7</v>
       </c>
     </row>
     <row r="11" spans="1:19">
@@ -3894,22 +3885,22 @@
         <v>85.7</v>
       </c>
       <c r="N11">
-        <v>93.2</v>
+        <v>93.8</v>
       </c>
       <c r="O11">
-        <v>90.90000000000001</v>
+        <v>93.8</v>
       </c>
       <c r="P11">
         <v>100</v>
       </c>
       <c r="Q11">
-        <v>93.90000000000001</v>
+        <v>95</v>
       </c>
       <c r="R11">
         <v>100</v>
       </c>
       <c r="S11">
-        <v>85.7</v>
+        <v>91.09999999999999</v>
       </c>
     </row>
     <row r="12" spans="1:19">
@@ -3953,7 +3944,7 @@
         <v>95.90000000000001</v>
       </c>
       <c r="N12">
-        <v>97.7</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="O12">
         <v>100</v>
@@ -3962,13 +3953,13 @@
         <v>100</v>
       </c>
       <c r="Q12">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="R12">
         <v>100</v>
       </c>
       <c r="S12">
-        <v>95.90000000000001</v>
+        <v>97.5</v>
       </c>
     </row>
     <row r="13" spans="1:19">
@@ -4012,7 +4003,7 @@
         <v>93.90000000000001</v>
       </c>
       <c r="N13">
-        <v>97.7</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="O13">
         <v>100</v>
@@ -4021,13 +4012,13 @@
         <v>100</v>
       </c>
       <c r="Q13">
-        <v>98</v>
+        <v>96.3</v>
       </c>
       <c r="R13">
         <v>100</v>
       </c>
       <c r="S13">
-        <v>93.90000000000001</v>
+        <v>96.2</v>
       </c>
     </row>
     <row r="14" spans="1:19">
@@ -4086,7 +4077,7 @@
         <v>100</v>
       </c>
       <c r="S14">
-        <v>98</v>
+        <v>98.7</v>
       </c>
     </row>
     <row r="15" spans="1:19">
@@ -4133,19 +4124,19 @@
         <v>100</v>
       </c>
       <c r="O15">
-        <v>97.7</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="P15">
         <v>100</v>
       </c>
       <c r="Q15">
-        <v>100</v>
+        <v>96.3</v>
       </c>
       <c r="R15">
         <v>100</v>
       </c>
       <c r="S15">
-        <v>91.8</v>
+        <v>94.90000000000001</v>
       </c>
     </row>
     <row r="16" spans="1:19">
@@ -4198,13 +4189,13 @@
         <v>100</v>
       </c>
       <c r="Q16">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="R16">
         <v>100</v>
       </c>
       <c r="S16">
-        <v>95.90000000000001</v>
+        <v>97.5</v>
       </c>
     </row>
     <row r="17" spans="1:19">
@@ -4248,22 +4239,22 @@
         <v>85.7</v>
       </c>
       <c r="N17">
-        <v>94.3</v>
+        <v>94.5</v>
       </c>
       <c r="O17">
-        <v>90.90000000000001</v>
+        <v>93.8</v>
       </c>
       <c r="P17">
         <v>100</v>
       </c>
       <c r="Q17">
-        <v>95.90000000000001</v>
+        <v>93.8</v>
       </c>
       <c r="R17">
         <v>100</v>
       </c>
       <c r="S17">
-        <v>85.7</v>
+        <v>91.09999999999999</v>
       </c>
     </row>
     <row r="18" spans="1:19">
@@ -4316,7 +4307,7 @@
         <v>100</v>
       </c>
       <c r="Q18">
-        <v>98</v>
+        <v>96.3</v>
       </c>
       <c r="R18">
         <v>100</v>
@@ -4375,13 +4366,13 @@
         <v>100</v>
       </c>
       <c r="Q19">
-        <v>95.90000000000001</v>
+        <v>96.3</v>
       </c>
       <c r="R19">
         <v>100</v>
       </c>
       <c r="S19">
-        <v>91.8</v>
+        <v>94.90000000000001</v>
       </c>
     </row>
     <row r="20" spans="1:19">
@@ -4425,22 +4416,22 @@
         <v>85.7</v>
       </c>
       <c r="N20">
-        <v>93.2</v>
+        <v>95.3</v>
       </c>
       <c r="O20">
-        <v>90.90000000000001</v>
+        <v>93.8</v>
       </c>
       <c r="P20">
         <v>100</v>
       </c>
       <c r="Q20">
-        <v>98</v>
+        <v>96.3</v>
       </c>
       <c r="R20">
         <v>100</v>
       </c>
       <c r="S20">
-        <v>85.7</v>
+        <v>91.09999999999999</v>
       </c>
     </row>
     <row r="21" spans="1:19">
@@ -4487,19 +4478,19 @@
         <v>97.7</v>
       </c>
       <c r="O21">
-        <v>95.5</v>
+        <v>95.3</v>
       </c>
       <c r="P21">
         <v>100</v>
       </c>
       <c r="Q21">
-        <v>100</v>
+        <v>98.8</v>
       </c>
       <c r="R21">
         <v>100</v>
       </c>
       <c r="S21">
-        <v>87.8</v>
+        <v>92.40000000000001</v>
       </c>
     </row>
     <row r="22" spans="1:19">
@@ -4602,7 +4593,7 @@
         <v>91.8</v>
       </c>
       <c r="N23">
-        <v>97.7</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="O23">
         <v>100</v>
@@ -4611,13 +4602,13 @@
         <v>100</v>
       </c>
       <c r="Q23">
-        <v>98</v>
+        <v>96.3</v>
       </c>
       <c r="R23">
         <v>100</v>
       </c>
       <c r="S23">
-        <v>91.8</v>
+        <v>94.90000000000001</v>
       </c>
     </row>
     <row r="24" spans="1:19">
@@ -4670,7 +4661,7 @@
         <v>100</v>
       </c>
       <c r="Q24">
-        <v>100</v>
+        <v>98.8</v>
       </c>
       <c r="R24">
         <v>100</v>
@@ -4720,7 +4711,7 @@
         <v>91.8</v>
       </c>
       <c r="N25">
-        <v>98.90000000000001</v>
+        <v>99.2</v>
       </c>
       <c r="O25">
         <v>100</v>
@@ -4729,13 +4720,13 @@
         <v>100</v>
       </c>
       <c r="Q25">
-        <v>95.90000000000001</v>
+        <v>95</v>
       </c>
       <c r="R25">
         <v>100</v>
       </c>
       <c r="S25">
-        <v>91.8</v>
+        <v>94.90000000000001</v>
       </c>
     </row>
     <row r="26" spans="1:19">
@@ -4779,22 +4770,22 @@
         <v>75.5</v>
       </c>
       <c r="N26">
+        <v>94.5</v>
+      </c>
+      <c r="O26">
+        <v>92.2</v>
+      </c>
+      <c r="P26">
+        <v>100</v>
+      </c>
+      <c r="Q26">
+        <v>91.3</v>
+      </c>
+      <c r="R26">
         <v>94.3</v>
       </c>
-      <c r="O26">
-        <v>90.90000000000001</v>
-      </c>
-      <c r="P26">
-        <v>100</v>
-      </c>
-      <c r="Q26">
-        <v>91.8</v>
-      </c>
-      <c r="R26">
-        <v>91.09999999999999</v>
-      </c>
       <c r="S26">
-        <v>75.5</v>
+        <v>84.8</v>
       </c>
     </row>
     <row r="27" spans="1:19">
@@ -4838,22 +4829,22 @@
         <v>77.59999999999999</v>
       </c>
       <c r="N27">
-        <v>94.3</v>
+        <v>94.5</v>
       </c>
       <c r="O27">
-        <v>90.90000000000001</v>
+        <v>92.2</v>
       </c>
       <c r="P27">
         <v>100</v>
       </c>
       <c r="Q27">
-        <v>95.90000000000001</v>
+        <v>93.8</v>
       </c>
       <c r="R27">
-        <v>93.3</v>
+        <v>95.7</v>
       </c>
       <c r="S27">
-        <v>77.59999999999999</v>
+        <v>86.09999999999999</v>
       </c>
     </row>
     <row r="28" spans="1:19">
@@ -4897,7 +4888,7 @@
         <v>87.8</v>
       </c>
       <c r="N28">
-        <v>97.7</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="O28">
         <v>100</v>
@@ -4906,13 +4897,13 @@
         <v>100</v>
       </c>
       <c r="Q28">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="R28">
         <v>100</v>
       </c>
       <c r="S28">
-        <v>87.8</v>
+        <v>92.40000000000001</v>
       </c>
     </row>
     <row r="29" spans="1:19">
@@ -4956,22 +4947,22 @@
         <v>83.7</v>
       </c>
       <c r="N29">
-        <v>94.3</v>
+        <v>94.5</v>
       </c>
       <c r="O29">
-        <v>90.90000000000001</v>
+        <v>93.8</v>
       </c>
       <c r="P29">
         <v>100</v>
       </c>
       <c r="Q29">
-        <v>91.8</v>
+        <v>95</v>
       </c>
       <c r="R29">
         <v>100</v>
       </c>
       <c r="S29">
-        <v>83.7</v>
+        <v>89.90000000000001</v>
       </c>
     </row>
     <row r="30" spans="1:19">
@@ -5027,10 +5018,10 @@
         <v>100</v>
       </c>
       <c r="R30">
-        <v>77.8</v>
+        <v>85.7</v>
       </c>
       <c r="S30">
-        <v>95.90000000000001</v>
+        <v>97.5</v>
       </c>
     </row>
     <row r="31" spans="1:19">
@@ -5083,7 +5074,7 @@
         <v>100</v>
       </c>
       <c r="Q31">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="R31">
         <v>100</v>
@@ -5142,13 +5133,13 @@
         <v>100</v>
       </c>
       <c r="Q32">
-        <v>100</v>
+        <v>98.8</v>
       </c>
       <c r="R32">
         <v>100</v>
       </c>
       <c r="S32">
-        <v>93.90000000000001</v>
+        <v>96.2</v>
       </c>
     </row>
     <row r="33" spans="1:19">
@@ -5201,13 +5192,13 @@
         <v>100</v>
       </c>
       <c r="Q33">
-        <v>95.90000000000001</v>
+        <v>97.5</v>
       </c>
       <c r="R33">
         <v>100</v>
       </c>
       <c r="S33">
-        <v>95.90000000000001</v>
+        <v>97.5</v>
       </c>
     </row>
     <row r="34" spans="1:19">
@@ -5251,22 +5242,22 @@
         <v>93.90000000000001</v>
       </c>
       <c r="N34">
-        <v>96.59999999999999</v>
+        <v>97.7</v>
       </c>
       <c r="O34">
-        <v>95.5</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="P34">
         <v>100</v>
       </c>
       <c r="Q34">
-        <v>95.90000000000001</v>
+        <v>95</v>
       </c>
       <c r="R34">
         <v>100</v>
       </c>
       <c r="S34">
-        <v>93.90000000000001</v>
+        <v>96.2</v>
       </c>
     </row>
     <row r="35" spans="1:19">
@@ -5319,13 +5310,13 @@
         <v>100</v>
       </c>
       <c r="Q35">
-        <v>100</v>
+        <v>98.8</v>
       </c>
       <c r="R35">
         <v>100</v>
       </c>
       <c r="S35">
-        <v>91.8</v>
+        <v>94.90000000000001</v>
       </c>
     </row>
     <row r="36" spans="1:19">
@@ -5378,13 +5369,13 @@
         <v>100</v>
       </c>
       <c r="Q36">
-        <v>100</v>
+        <v>98.8</v>
       </c>
       <c r="R36">
         <v>100</v>
       </c>
       <c r="S36">
-        <v>91.8</v>
+        <v>94.90000000000001</v>
       </c>
     </row>
     <row r="37" spans="1:19">
@@ -5437,7 +5428,7 @@
         <v>100</v>
       </c>
       <c r="Q37">
-        <v>100</v>
+        <v>98.8</v>
       </c>
       <c r="R37">
         <v>100</v>
@@ -5509,19 +5500,19 @@
         <v>34</v>
       </c>
       <c r="D2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F2" s="2">
-        <v>97.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="G2" s="2">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="H2">
-        <v>8.5</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -5617,7 +5608,7 @@
         <v>0</v>
       </c>
       <c r="H5">
-        <v>9.4</v>
+        <v>9.1</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -5731,7 +5722,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5761,29 +5752,6 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
-      <c r="A2">
-        <v>20330051920236</v>
-      </c>
-      <c r="B2" t="s">
-        <v>67</v>
-      </c>
-      <c r="C2" t="s">
-        <v>68</v>
-      </c>
-      <c r="D2" t="s">
-        <v>69</v>
-      </c>
-      <c r="E2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F2" t="s">
-        <v>58</v>
-      </c>
-      <c r="G2">
-        <v>5</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
